--- a/Design Files/Driver-Main-Board-v1.0/BOM/eSpark-BOM-Driver-Main-Board-v1.0.xlsx
+++ b/Design Files/Driver-Main-Board-v1.0/BOM/eSpark-BOM-Driver-Main-Board-v1.0.xlsx
@@ -15,14 +15,14 @@
     <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="LCSC">'5 Boards'!$O$14:$O$92</definedName>
+    <definedName name="LCSC">'5 Boards'!$O$14:$O$98</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="593">
   <si>
     <t>Component list</t>
   </si>
@@ -111,9 +111,6 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>C1, C2, C3</t>
-  </si>
-  <si>
     <t>C4</t>
   </si>
   <si>
@@ -192,9 +189,6 @@
     <t>F1, F2, F3, F4, F5, F6</t>
   </si>
   <si>
-    <t>FB1, FB2, FB3, FB4</t>
-  </si>
-  <si>
     <t>J1</t>
   </si>
   <si>
@@ -216,9 +210,6 @@
     <t>J8</t>
   </si>
   <si>
-    <t>J9, J10, J11, J12, J15, J16</t>
-  </si>
-  <si>
     <t>J13, J14</t>
   </si>
   <si>
@@ -279,9 +270,6 @@
     <t>R27</t>
   </si>
   <si>
-    <t>R28, R29, R64, R65, R66, R67, R68, R69, R70, R71, R72, R73, R74, R75, R86, R87, R89</t>
-  </si>
-  <si>
     <t>R30, R31</t>
   </si>
   <si>
@@ -1723,6 +1711,96 @@
   </si>
   <si>
     <t>C49257</t>
+  </si>
+  <si>
+    <t>C1, C2</t>
+  </si>
+  <si>
+    <t>D22</t>
+  </si>
+  <si>
+    <t>DIODE SCHOTTKY 60V 5A SMA</t>
+  </si>
+  <si>
+    <t>SMA</t>
+  </si>
+  <si>
+    <t>SS56</t>
+  </si>
+  <si>
+    <t>FB1, FB2, FB3, FB4, FB5</t>
+  </si>
+  <si>
+    <t>J9, J10, J11, J12, J15, J16, J35</t>
+  </si>
+  <si>
+    <t>R28, R29, R64, R65, R66, R67, R68, R69, R70, R71, R72, R73, R74, R75, R86, R87, R89, R112</t>
+  </si>
+  <si>
+    <t>R113</t>
+  </si>
+  <si>
+    <t>Jumper</t>
+  </si>
+  <si>
+    <t>P=2.54mm Shunts, Jumpers ROHS</t>
+  </si>
+  <si>
+    <t>X2541-A1NIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XKB </t>
+  </si>
+  <si>
+    <t>32V 1kA Blade fuse 2A Automotive Fuses ROHS</t>
+  </si>
+  <si>
+    <t>0287002.PXCN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Littelfuse </t>
+  </si>
+  <si>
+    <t>Ethernet Cable</t>
+  </si>
+  <si>
+    <t>Cat6 Gigabit Ethernet Cable 1m Cable/ModularCable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UGREEN </t>
+  </si>
+  <si>
+    <t>Network cables</t>
+  </si>
+  <si>
+    <t>LDR254-100726-300-4P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEALON </t>
+  </si>
+  <si>
+    <t>LDS254-100726-300-2P</t>
+  </si>
+  <si>
+    <t>C65009</t>
+  </si>
+  <si>
+    <t>Resistors</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>C2938578</t>
+  </si>
+  <si>
+    <t>C142680</t>
+  </si>
+  <si>
+    <t>C3015021</t>
+  </si>
+  <si>
+    <t>C2999043</t>
   </si>
 </sst>
 </file>
@@ -2114,7 +2192,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2219,17 +2297,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2264,6 +2331,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2554,7 +2635,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R106"/>
+  <dimension ref="A1:R113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
@@ -2574,6 +2655,9 @@
     <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" thickBot="1">
@@ -2587,14 +2671,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
@@ -2605,7 +2689,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="40" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
@@ -2629,7 +2713,7 @@
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="41" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="G3" s="29"/>
       <c r="H3" s="30"/>
@@ -2716,46 +2800,46 @@
         <v>28</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="M7" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q7" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="R7" s="12" t="s">
         <v>473</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q7" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="R7" s="12" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -2768,83 +2852,83 @@
         <v>6</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>29</v>
+        <v>563</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="I8" s="55" t="s">
-        <v>561</v>
+        <v>311</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="K8" s="45" t="s">
-        <v>425</v>
+        <v>348</v>
+      </c>
+      <c r="K8" s="42" t="s">
+        <v>421</v>
       </c>
       <c r="L8" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8" s="14">
         <f>L8*5</f>
+        <v>10</v>
+      </c>
+      <c r="N8" s="14">
         <v>15</v>
       </c>
-      <c r="N8" s="14">
-        <v>20</v>
-      </c>
-      <c r="O8" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P8" s="49" t="s">
-        <v>479</v>
+      <c r="O8" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P8" s="46" t="s">
+        <v>475</v>
       </c>
       <c r="Q8" s="15">
         <f>P8*N8</f>
-        <v>5.8620000000000001</v>
+        <v>4.3965000000000005</v>
       </c>
       <c r="R8" s="14"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B91" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B92" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="22" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I9" s="55" t="s">
-        <v>561</v>
+        <v>312</v>
+      </c>
+      <c r="I9" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="K9" s="46" t="s">
-        <v>426</v>
+        <v>349</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>422</v>
       </c>
       <c r="L9" s="20">
         <v>1</v>
@@ -2856,11 +2940,11 @@
       <c r="N9" s="14">
         <v>10</v>
       </c>
-      <c r="O9" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P9" s="49" t="s">
-        <v>480</v>
+      <c r="O9" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P9" s="46" t="s">
+        <v>476</v>
       </c>
       <c r="Q9" s="21">
         <f t="shared" ref="Q9" si="2">P9*N9</f>
@@ -2878,28 +2962,28 @@
         <v>6</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="I10" s="55" t="s">
-        <v>561</v>
+        <v>313</v>
+      </c>
+      <c r="I10" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="K10" s="45" t="s">
-        <v>427</v>
+        <v>350</v>
+      </c>
+      <c r="K10" s="42" t="s">
+        <v>423</v>
       </c>
       <c r="L10" s="14">
         <v>21</v>
@@ -2909,13 +2993,13 @@
         <v>105</v>
       </c>
       <c r="N10" s="14" t="s">
-        <v>543</v>
-      </c>
-      <c r="O10" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P10" s="49" t="s">
-        <v>481</v>
+        <v>539</v>
+      </c>
+      <c r="O10" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P10" s="46" t="s">
+        <v>477</v>
       </c>
       <c r="Q10" s="15">
         <f>P10*N10</f>
@@ -2933,28 +3017,28 @@
         <v>6</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="I11" s="55" t="s">
-        <v>561</v>
+        <v>313</v>
+      </c>
+      <c r="I11" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>355</v>
-      </c>
-      <c r="K11" s="46" t="s">
-        <v>428</v>
+        <v>351</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>424</v>
       </c>
       <c r="L11" s="20">
         <v>1</v>
@@ -2966,11 +3050,11 @@
       <c r="N11" s="14">
         <v>10</v>
       </c>
-      <c r="O11" s="50" t="s">
+      <c r="O11" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P11" s="46" t="s">
         <v>478</v>
-      </c>
-      <c r="P11" s="49" t="s">
-        <v>482</v>
       </c>
       <c r="Q11" s="21">
         <f t="shared" ref="Q11" si="4">P11*N11</f>
@@ -2988,28 +3072,28 @@
         <v>6</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="I12" s="55" t="s">
-        <v>561</v>
+        <v>314</v>
+      </c>
+      <c r="I12" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="K12" s="45" t="s">
-        <v>429</v>
+        <v>352</v>
+      </c>
+      <c r="K12" s="42" t="s">
+        <v>425</v>
       </c>
       <c r="L12" s="14">
         <v>1</v>
@@ -3019,13 +3103,13 @@
         <v>5</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>544</v>
-      </c>
-      <c r="O12" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P12" s="49" t="s">
-        <v>483</v>
+        <v>540</v>
+      </c>
+      <c r="O12" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P12" s="46" t="s">
+        <v>479</v>
       </c>
       <c r="Q12" s="15">
         <f>P12*N12</f>
@@ -3043,28 +3127,28 @@
         <v>6</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I13" s="55" t="s">
-        <v>561</v>
+        <v>312</v>
+      </c>
+      <c r="I13" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>357</v>
-      </c>
-      <c r="K13" s="46" t="s">
-        <v>430</v>
+        <v>353</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>426</v>
       </c>
       <c r="L13" s="20">
         <v>2</v>
@@ -3076,11 +3160,11 @@
       <c r="N13" s="14">
         <v>20</v>
       </c>
-      <c r="O13" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P13" s="49" t="s">
-        <v>484</v>
+      <c r="O13" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P13" s="46" t="s">
+        <v>480</v>
       </c>
       <c r="Q13" s="21">
         <f t="shared" ref="Q13" si="6">P13*N13</f>
@@ -3098,28 +3182,28 @@
         <v>6</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="I14" s="55" t="s">
-        <v>561</v>
+        <v>312</v>
+      </c>
+      <c r="I14" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="K14" s="45" t="s">
-        <v>431</v>
+        <v>354</v>
+      </c>
+      <c r="K14" s="42" t="s">
+        <v>427</v>
       </c>
       <c r="L14" s="14">
         <v>2</v>
@@ -3129,13 +3213,13 @@
         <v>10</v>
       </c>
       <c r="N14" s="14" t="s">
-        <v>544</v>
-      </c>
-      <c r="O14" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P14" s="49" t="s">
-        <v>485</v>
+        <v>540</v>
+      </c>
+      <c r="O14" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P14" s="46" t="s">
+        <v>481</v>
       </c>
       <c r="Q14" s="15">
         <f>P14*N14</f>
@@ -3153,28 +3237,28 @@
         <v>6</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I15" s="55" t="s">
-        <v>561</v>
+        <v>312</v>
+      </c>
+      <c r="I15" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="K15" s="46" t="s">
-        <v>432</v>
+        <v>355</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>428</v>
       </c>
       <c r="L15" s="20">
         <v>4</v>
@@ -3184,13 +3268,13 @@
         <v>20</v>
       </c>
       <c r="N15" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O15" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P15" s="49" t="s">
-        <v>486</v>
+        <v>542</v>
+      </c>
+      <c r="O15" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P15" s="46" t="s">
+        <v>482</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" ref="Q15" si="8">P15*N15</f>
@@ -3207,51 +3291,51 @@
       <c r="C16" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>123</v>
-      </c>
-      <c r="F16" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="G16" s="48" t="s">
-        <v>249</v>
-      </c>
-      <c r="H16" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="I16" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J16" s="48" t="s">
-        <v>360</v>
-      </c>
-      <c r="K16" s="47" t="s">
-        <v>433</v>
-      </c>
-      <c r="L16" s="48">
+      <c r="D16" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="G16" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="H16" s="45" t="s">
+        <v>312</v>
+      </c>
+      <c r="I16" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J16" s="45" t="s">
+        <v>356</v>
+      </c>
+      <c r="K16" s="44" t="s">
+        <v>429</v>
+      </c>
+      <c r="L16" s="45">
         <v>2</v>
       </c>
-      <c r="M16" s="48">
+      <c r="M16" s="45">
         <f>L16*5</f>
         <v>10</v>
       </c>
-      <c r="N16" s="48" t="s">
-        <v>468</v>
-      </c>
-      <c r="O16" s="52" t="s">
-        <v>478</v>
-      </c>
-      <c r="P16" s="53" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q16" s="54" t="s">
-        <v>468</v>
-      </c>
-      <c r="R16" s="51" t="s">
-        <v>560</v>
+      <c r="N16" s="45" t="s">
+        <v>464</v>
+      </c>
+      <c r="O16" s="49" t="s">
+        <v>474</v>
+      </c>
+      <c r="P16" s="50" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q16" s="51" t="s">
+        <v>464</v>
+      </c>
+      <c r="R16" s="48" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -3264,28 +3348,28 @@
         <v>6</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I17" s="55" t="s">
-        <v>561</v>
+        <v>312</v>
+      </c>
+      <c r="I17" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>361</v>
-      </c>
-      <c r="K17" s="46" t="s">
-        <v>431</v>
+        <v>357</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>427</v>
       </c>
       <c r="L17" s="20">
         <v>1</v>
@@ -3295,13 +3379,13 @@
         <v>5</v>
       </c>
       <c r="N17" s="14" t="s">
-        <v>547</v>
-      </c>
-      <c r="O17" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P17" s="49" t="s">
-        <v>487</v>
+        <v>543</v>
+      </c>
+      <c r="O17" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P17" s="46" t="s">
+        <v>483</v>
       </c>
       <c r="Q17" s="21">
         <f t="shared" ref="Q17" si="10">P17*N17</f>
@@ -3319,28 +3403,28 @@
         <v>6</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="I18" s="55" t="s">
-        <v>561</v>
+        <v>312</v>
+      </c>
+      <c r="I18" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="K18" s="45" t="s">
-        <v>428</v>
+        <v>358</v>
+      </c>
+      <c r="K18" s="42" t="s">
+        <v>424</v>
       </c>
       <c r="L18" s="14">
         <v>6</v>
@@ -3350,13 +3434,13 @@
         <v>30</v>
       </c>
       <c r="N18" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O18" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P18" s="49" t="s">
-        <v>488</v>
+        <v>542</v>
+      </c>
+      <c r="O18" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P18" s="46" t="s">
+        <v>484</v>
       </c>
       <c r="Q18" s="15">
         <f>P18*N18</f>
@@ -3374,28 +3458,28 @@
         <v>6</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I19" s="55" t="s">
-        <v>561</v>
+        <v>312</v>
+      </c>
+      <c r="I19" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="K19" s="46" t="s">
-        <v>434</v>
+        <v>359</v>
+      </c>
+      <c r="K19" s="43" t="s">
+        <v>430</v>
       </c>
       <c r="L19" s="20">
         <v>1</v>
@@ -3405,13 +3489,13 @@
         <v>5</v>
       </c>
       <c r="N19" s="14" t="s">
-        <v>544</v>
-      </c>
-      <c r="O19" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P19" s="49" t="s">
-        <v>489</v>
+        <v>540</v>
+      </c>
+      <c r="O19" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P19" s="46" t="s">
+        <v>485</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" ref="Q19" si="12">P19*N19</f>
@@ -3429,28 +3513,28 @@
         <v>6</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="I20" s="55" t="s">
-        <v>561</v>
+        <v>312</v>
+      </c>
+      <c r="I20" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>550</v>
-      </c>
-      <c r="K20" s="45" t="s">
-        <v>434</v>
+        <v>546</v>
+      </c>
+      <c r="K20" s="42" t="s">
+        <v>430</v>
       </c>
       <c r="L20" s="14">
         <v>2</v>
@@ -3460,13 +3544,13 @@
         <v>10</v>
       </c>
       <c r="N20" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O20" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P20" s="49" t="s">
-        <v>490</v>
+        <v>542</v>
+      </c>
+      <c r="O20" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P20" s="46" t="s">
+        <v>486</v>
       </c>
       <c r="Q20" s="15">
         <f>P20*N20</f>
@@ -3484,28 +3568,28 @@
         <v>6</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="I21" s="55" t="s">
-        <v>561</v>
+        <v>314</v>
+      </c>
+      <c r="I21" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="K21" s="46" t="s">
-        <v>435</v>
+        <v>360</v>
+      </c>
+      <c r="K21" s="43" t="s">
+        <v>431</v>
       </c>
       <c r="L21" s="20">
         <v>7</v>
@@ -3515,13 +3599,13 @@
         <v>35</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>547</v>
-      </c>
-      <c r="O21" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P21" s="49" t="s">
-        <v>491</v>
+        <v>543</v>
+      </c>
+      <c r="O21" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P21" s="46" t="s">
+        <v>487</v>
       </c>
       <c r="Q21" s="21">
         <f t="shared" ref="Q21" si="14">P21*N21</f>
@@ -3539,28 +3623,28 @@
         <v>6</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="I22" s="55" t="s">
-        <v>561</v>
+        <v>312</v>
+      </c>
+      <c r="I22" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="K22" s="45" t="s">
-        <v>436</v>
+        <v>361</v>
+      </c>
+      <c r="K22" s="42" t="s">
+        <v>432</v>
       </c>
       <c r="L22" s="14">
         <v>1</v>
@@ -3570,13 +3654,13 @@
         <v>5</v>
       </c>
       <c r="N22" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O22" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P22" s="49" t="s">
-        <v>492</v>
+        <v>542</v>
+      </c>
+      <c r="O22" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P22" s="46" t="s">
+        <v>488</v>
       </c>
       <c r="Q22" s="15">
         <f>P22*N22</f>
@@ -3594,28 +3678,28 @@
         <v>6</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="I23" s="55" t="s">
-        <v>561</v>
+        <v>315</v>
+      </c>
+      <c r="I23" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>366</v>
-      </c>
-      <c r="K23" s="46" t="s">
-        <v>437</v>
+        <v>362</v>
+      </c>
+      <c r="K23" s="43" t="s">
+        <v>433</v>
       </c>
       <c r="L23" s="20">
         <v>1</v>
@@ -3625,13 +3709,13 @@
         <v>5</v>
       </c>
       <c r="N23" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O23" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P23" s="49" t="s">
-        <v>493</v>
+        <v>542</v>
+      </c>
+      <c r="O23" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P23" s="46" t="s">
+        <v>489</v>
       </c>
       <c r="Q23" s="21">
         <f t="shared" ref="Q23" si="16">P23*N23</f>
@@ -3649,28 +3733,28 @@
         <v>6</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="I24" s="55" t="s">
-        <v>561</v>
+        <v>314</v>
+      </c>
+      <c r="I24" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="K24" s="45" t="s">
-        <v>438</v>
+        <v>363</v>
+      </c>
+      <c r="K24" s="42" t="s">
+        <v>434</v>
       </c>
       <c r="L24" s="14">
         <v>8</v>
@@ -3680,13 +3764,13 @@
         <v>40</v>
       </c>
       <c r="N24" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O24" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P24" s="49" t="s">
-        <v>486</v>
+        <v>542</v>
+      </c>
+      <c r="O24" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P24" s="46" t="s">
+        <v>482</v>
       </c>
       <c r="Q24" s="15">
         <f>P24*N24</f>
@@ -3704,28 +3788,28 @@
         <v>6</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I25" s="55" t="s">
-        <v>561</v>
+        <v>312</v>
+      </c>
+      <c r="I25" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="K25" s="46" t="s">
-        <v>439</v>
+        <v>364</v>
+      </c>
+      <c r="K25" s="43" t="s">
+        <v>435</v>
       </c>
       <c r="L25" s="20">
         <v>2</v>
@@ -3735,13 +3819,13 @@
         <v>10</v>
       </c>
       <c r="N25" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O25" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P25" s="49" t="s">
-        <v>494</v>
+        <v>542</v>
+      </c>
+      <c r="O25" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P25" s="46" t="s">
+        <v>490</v>
       </c>
       <c r="Q25" s="21">
         <f t="shared" ref="Q25" si="18">P25*N25</f>
@@ -3759,28 +3843,28 @@
         <v>7</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="I26" s="55" t="s">
-        <v>561</v>
+        <v>316</v>
+      </c>
+      <c r="I26" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>551</v>
-      </c>
-      <c r="K26" s="45" t="s">
-        <v>468</v>
+        <v>547</v>
+      </c>
+      <c r="K26" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L26" s="14">
         <v>1</v>
@@ -3792,11 +3876,11 @@
       <c r="N26" s="14">
         <v>10</v>
       </c>
-      <c r="O26" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P26" s="49" t="s">
-        <v>495</v>
+      <c r="O26" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P26" s="46" t="s">
+        <v>491</v>
       </c>
       <c r="Q26" s="15">
         <f>P26*N26</f>
@@ -3814,28 +3898,28 @@
         <v>8</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="I27" s="55" t="s">
-        <v>561</v>
+        <v>317</v>
+      </c>
+      <c r="I27" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="K27" s="45" t="s">
-        <v>468</v>
+        <v>365</v>
+      </c>
+      <c r="K27" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L27" s="20">
         <v>2</v>
@@ -3845,13 +3929,13 @@
         <v>10</v>
       </c>
       <c r="N27" s="14" t="s">
-        <v>544</v>
-      </c>
-      <c r="O27" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P27" s="49" t="s">
-        <v>496</v>
+        <v>540</v>
+      </c>
+      <c r="O27" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P27" s="46" t="s">
+        <v>492</v>
       </c>
       <c r="Q27" s="21">
         <f t="shared" ref="Q27" si="20">P27*N27</f>
@@ -3869,28 +3953,28 @@
         <v>7</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="I28" s="55" t="s">
-        <v>561</v>
+        <v>318</v>
+      </c>
+      <c r="I28" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="K28" s="45" t="s">
-        <v>468</v>
+        <v>548</v>
+      </c>
+      <c r="K28" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L28" s="14">
         <v>8</v>
@@ -3900,13 +3984,13 @@
         <v>40</v>
       </c>
       <c r="N28" s="14" t="s">
-        <v>547</v>
-      </c>
-      <c r="O28" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P28" s="49" t="s">
-        <v>497</v>
+        <v>543</v>
+      </c>
+      <c r="O28" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P28" s="46" t="s">
+        <v>493</v>
       </c>
       <c r="Q28" s="15">
         <f>P28*N28</f>
@@ -3924,28 +4008,28 @@
         <v>7</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="I29" s="55" t="s">
-        <v>561</v>
+        <v>319</v>
+      </c>
+      <c r="I29" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>370</v>
-      </c>
-      <c r="K29" s="45" t="s">
-        <v>468</v>
+        <v>366</v>
+      </c>
+      <c r="K29" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L29" s="20">
         <v>2</v>
@@ -3957,11 +4041,11 @@
       <c r="N29" s="14">
         <v>15</v>
       </c>
-      <c r="O29" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P29" s="49" t="s">
-        <v>498</v>
+      <c r="O29" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P29" s="46" t="s">
+        <v>494</v>
       </c>
       <c r="Q29" s="21">
         <f t="shared" ref="Q29" si="22">P29*N29</f>
@@ -3979,28 +4063,28 @@
         <v>7</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="I30" s="55" t="s">
-        <v>561</v>
+        <v>320</v>
+      </c>
+      <c r="I30" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>553</v>
-      </c>
-      <c r="K30" s="45" t="s">
-        <v>468</v>
+        <v>549</v>
+      </c>
+      <c r="K30" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L30" s="14">
         <v>2</v>
@@ -4010,13 +4094,13 @@
         <v>10</v>
       </c>
       <c r="N30" s="14" t="s">
-        <v>544</v>
-      </c>
-      <c r="O30" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P30" s="49" t="s">
-        <v>499</v>
+        <v>540</v>
+      </c>
+      <c r="O30" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P30" s="46" t="s">
+        <v>495</v>
       </c>
       <c r="Q30" s="15">
         <f>P30*N30</f>
@@ -4034,28 +4118,28 @@
         <v>9</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="I31" s="55" t="s">
-        <v>561</v>
+        <v>321</v>
+      </c>
+      <c r="I31" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>371</v>
-      </c>
-      <c r="K31" s="45" t="s">
-        <v>468</v>
+        <v>367</v>
+      </c>
+      <c r="K31" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L31" s="20">
         <v>2</v>
@@ -4067,11 +4151,11 @@
       <c r="N31" s="14">
         <v>15</v>
       </c>
-      <c r="O31" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P31" s="49" t="s">
-        <v>500</v>
+      <c r="O31" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P31" s="46" t="s">
+        <v>496</v>
       </c>
       <c r="Q31" s="21">
         <f t="shared" ref="Q31" si="24">P31*N31</f>
@@ -4089,28 +4173,28 @@
         <v>7</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="I32" s="55" t="s">
-        <v>561</v>
+        <v>322</v>
+      </c>
+      <c r="I32" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>372</v>
-      </c>
-      <c r="K32" s="45" t="s">
-        <v>468</v>
+        <v>368</v>
+      </c>
+      <c r="K32" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L32" s="14">
         <v>2</v>
@@ -4122,11 +4206,11 @@
       <c r="N32" s="14">
         <v>20</v>
       </c>
-      <c r="O32" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P32" s="49" t="s">
-        <v>501</v>
+      <c r="O32" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P32" s="46" t="s">
+        <v>497</v>
       </c>
       <c r="Q32" s="15">
         <f>P32*N32</f>
@@ -4144,160 +4228,160 @@
         <v>9</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="I33" s="55" t="s">
-        <v>561</v>
+        <v>323</v>
+      </c>
+      <c r="I33" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="K33" s="45" t="s">
-        <v>468</v>
+        <v>369</v>
+      </c>
+      <c r="K33" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L33" s="20">
         <v>2</v>
       </c>
       <c r="M33" s="20">
-        <f t="shared" ref="M33" si="25">L33*5</f>
+        <f t="shared" ref="M33:M34" si="25">L33*5</f>
         <v>10</v>
       </c>
       <c r="N33" s="14">
         <v>15</v>
       </c>
-      <c r="O33" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P33" s="49" t="s">
-        <v>502</v>
+      <c r="O33" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P33" s="46" t="s">
+        <v>498</v>
       </c>
       <c r="Q33" s="21">
-        <f t="shared" ref="Q33" si="26">P33*N33</f>
+        <f t="shared" ref="Q33:Q34" si="26">P33*N33</f>
         <v>1.6214999999999999</v>
       </c>
       <c r="R33" s="20"/>
     </row>
-    <row r="34" spans="1:18" ht="24">
+    <row r="34" spans="1:18">
       <c r="A34" s="1"/>
       <c r="B34" s="16">
         <f>ROW(B34) - ROW($B$7)</f>
         <v>27</v>
       </c>
       <c r="C34" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>564</v>
+      </c>
+      <c r="E34" s="42" t="s">
+        <v>565</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>566</v>
+      </c>
+      <c r="G34" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="I34" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="K34" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L34" s="14">
+        <v>1</v>
+      </c>
+      <c r="M34" s="14">
+        <f t="shared" si="25"/>
+        <v>5</v>
+      </c>
+      <c r="N34" s="14">
         <v>10</v>
       </c>
-      <c r="D34" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="I34" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="K34" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L34" s="14">
-        <v>6</v>
-      </c>
-      <c r="M34" s="14">
-        <f>L34*5</f>
-        <v>30</v>
-      </c>
-      <c r="N34" s="14">
-        <v>40</v>
-      </c>
-      <c r="O34" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P34" s="49" t="s">
-        <v>503</v>
-      </c>
-      <c r="Q34" s="15">
-        <f>P34*N34</f>
-        <v>2.2279999999999998</v>
+      <c r="O34" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P34" s="46">
+        <v>4.53E-2</v>
+      </c>
+      <c r="Q34" s="21">
+        <f t="shared" si="26"/>
+        <v>0.45300000000000001</v>
       </c>
       <c r="R34" s="14"/>
     </row>
-    <row r="35" spans="1:18">
+    <row r="35" spans="1:18" ht="24">
       <c r="A35" s="1"/>
       <c r="B35" s="17">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C35" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="H35" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="I35" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J35" s="20" t="s">
-        <v>375</v>
-      </c>
-      <c r="K35" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L35" s="20">
-        <v>4</v>
-      </c>
-      <c r="M35" s="20">
-        <f t="shared" ref="M35" si="27">L35*5</f>
-        <v>20</v>
-      </c>
-      <c r="N35" s="14" t="s">
-        <v>547</v>
-      </c>
-      <c r="O35" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P35" s="49" t="s">
-        <v>504</v>
-      </c>
-      <c r="Q35" s="21">
-        <f t="shared" ref="Q35" si="28">P35*N35</f>
-        <v>0.38500000000000001</v>
-      </c>
-      <c r="R35" s="20"/>
+      <c r="C35" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="I35" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="K35" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L35" s="14">
+        <v>6</v>
+      </c>
+      <c r="M35" s="14">
+        <f>L35*5</f>
+        <v>30</v>
+      </c>
+      <c r="N35" s="14">
+        <v>40</v>
+      </c>
+      <c r="O35" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P35" s="46" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q35" s="15">
+        <f>P35*N35</f>
+        <v>2.2279999999999998</v>
+      </c>
+      <c r="R35" s="14"/>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="1"/>
@@ -4305,54 +4389,54 @@
         <f>ROW(B36) - ROW($B$7)</f>
         <v>29</v>
       </c>
-      <c r="C36" s="22" t="s">
-        <v>12</v>
+      <c r="C36" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="G36" s="14">
-        <v>1715721</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>328</v>
-      </c>
-      <c r="I36" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>554</v>
-      </c>
-      <c r="K36" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L36" s="14">
-        <v>1</v>
-      </c>
-      <c r="M36" s="14">
-        <f>L36*5</f>
+        <v>568</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="I36" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="K36" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L36" s="20">
         <v>5</v>
       </c>
-      <c r="N36" s="14">
-        <v>6</v>
-      </c>
-      <c r="O36" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P36" s="49" t="s">
-        <v>505</v>
-      </c>
-      <c r="Q36" s="15">
-        <f>P36*N36</f>
-        <v>2.3418000000000001</v>
-      </c>
-      <c r="R36" s="14"/>
+      <c r="M36" s="20">
+        <f t="shared" ref="M36" si="27">L36*5</f>
+        <v>25</v>
+      </c>
+      <c r="N36" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="O36" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P36" s="46" t="s">
+        <v>500</v>
+      </c>
+      <c r="Q36" s="21">
+        <f t="shared" ref="Q36" si="28">P36*N36</f>
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="R36" s="20"/>
     </row>
     <row r="37" spans="1:18">
       <c r="A37" s="1"/>
@@ -4360,329 +4444,329 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C37" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>144</v>
+      <c r="C37" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>139</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="H37" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="I37" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J37" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="K37" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L37" s="20">
+        <v>465</v>
+      </c>
+      <c r="G37" s="14">
+        <v>1715721</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="I37" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>550</v>
+      </c>
+      <c r="K37" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L37" s="14">
         <v>1</v>
       </c>
-      <c r="M37" s="20">
-        <f t="shared" ref="M37" si="29">L37*5</f>
+      <c r="M37" s="14">
+        <f>L37*5</f>
         <v>5</v>
       </c>
       <c r="N37" s="14">
         <v>6</v>
       </c>
-      <c r="O37" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P37" s="49" t="s">
-        <v>506</v>
-      </c>
-      <c r="Q37" s="21">
-        <f t="shared" ref="Q37" si="30">P37*N37</f>
-        <v>7.3452000000000002</v>
-      </c>
-      <c r="R37" s="20"/>
-    </row>
-    <row r="38" spans="1:18" ht="48">
+      <c r="O37" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P37" s="46" t="s">
+        <v>501</v>
+      </c>
+      <c r="Q37" s="15">
+        <f>P37*N37</f>
+        <v>2.3418000000000001</v>
+      </c>
+      <c r="R37" s="14"/>
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38" s="1"/>
       <c r="B38" s="16">
         <f>ROW(B38) - ROW($B$7)</f>
         <v>31</v>
       </c>
-      <c r="C38" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>145</v>
+      <c r="C38" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>140</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="I38" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>377</v>
-      </c>
-      <c r="K38" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L38" s="14">
-        <v>2</v>
-      </c>
-      <c r="M38" s="14">
-        <f>L38*5</f>
-        <v>10</v>
+        <v>465</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="I38" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="K38" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L38" s="20">
+        <v>1</v>
+      </c>
+      <c r="M38" s="20">
+        <f t="shared" ref="M38" si="29">L38*5</f>
+        <v>5</v>
       </c>
       <c r="N38" s="14">
-        <v>20</v>
-      </c>
-      <c r="O38" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P38" s="49" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q38" s="15">
-        <f>P38*N38</f>
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="R38" s="14"/>
-    </row>
-    <row r="39" spans="1:18">
+        <v>6</v>
+      </c>
+      <c r="O38" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P38" s="46" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q38" s="21">
+        <f t="shared" ref="Q38" si="30">P38*N38</f>
+        <v>7.3452000000000002</v>
+      </c>
+      <c r="R38" s="20"/>
+    </row>
+    <row r="39" spans="1:18" ht="48">
       <c r="A39" s="1"/>
       <c r="B39" s="17">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C39" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="G39" s="56" t="s">
-        <v>440</v>
-      </c>
-      <c r="H39" s="20" t="s">
-        <v>565</v>
-      </c>
-      <c r="I39" s="55" t="s">
-        <v>564</v>
-      </c>
-      <c r="J39" s="20" t="s">
-        <v>566</v>
-      </c>
-      <c r="K39" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L39" s="20">
-        <v>1</v>
-      </c>
-      <c r="M39" s="20">
-        <f t="shared" ref="M39" si="31">L39*5</f>
-        <v>5</v>
+      <c r="D39" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="I39" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="K39" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L39" s="14">
+        <v>2</v>
+      </c>
+      <c r="M39" s="14">
+        <f>L39*5</f>
+        <v>10</v>
       </c>
       <c r="N39" s="14">
-        <v>50</v>
-      </c>
-      <c r="O39" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P39" s="49">
-        <v>1.46E-2</v>
-      </c>
-      <c r="Q39" s="21">
-        <f t="shared" ref="Q39" si="32">P39*N39</f>
-        <v>0.73</v>
-      </c>
-      <c r="R39" s="20"/>
-    </row>
-    <row r="40" spans="1:18" ht="24">
+        <v>20</v>
+      </c>
+      <c r="O39" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P39" s="46" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q39" s="15">
+        <f>P39*N39</f>
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="R39" s="14"/>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40" s="1"/>
       <c r="B40" s="16">
         <f>ROW(B40) - ROW($B$7)</f>
         <v>33</v>
       </c>
-      <c r="C40" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="I40" s="55" t="s">
+      <c r="C40" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="G40" s="53" t="s">
+        <v>436</v>
+      </c>
+      <c r="H40" s="20" t="s">
         <v>561</v>
       </c>
-      <c r="J40" s="14" t="s">
-        <v>378</v>
-      </c>
-      <c r="K40" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L40" s="14">
+      <c r="I40" s="52" t="s">
+        <v>560</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>562</v>
+      </c>
+      <c r="K40" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L40" s="20">
         <v>1</v>
       </c>
-      <c r="M40" s="14">
-        <f>L40*5</f>
+      <c r="M40" s="20">
+        <f t="shared" ref="M40" si="31">L40*5</f>
         <v>5</v>
       </c>
       <c r="N40" s="14">
-        <v>10</v>
-      </c>
-      <c r="O40" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P40" s="49" t="s">
-        <v>508</v>
-      </c>
-      <c r="Q40" s="15">
-        <f>P40*N40</f>
-        <v>1.61</v>
-      </c>
-      <c r="R40" s="14"/>
-    </row>
-    <row r="41" spans="1:18">
+        <v>50</v>
+      </c>
+      <c r="O40" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P40" s="46">
+        <v>1.46E-2</v>
+      </c>
+      <c r="Q40" s="21">
+        <f t="shared" ref="Q40" si="32">P40*N40</f>
+        <v>0.73</v>
+      </c>
+      <c r="R40" s="20"/>
+    </row>
+    <row r="41" spans="1:18" ht="24">
       <c r="A41" s="1"/>
       <c r="B41" s="17">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C41" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>148</v>
+      <c r="C41" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>143</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="H41" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="I41" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J41" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="K41" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L41" s="20">
+        <v>465</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="I41" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="K41" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L41" s="14">
         <v>1</v>
       </c>
-      <c r="M41" s="20">
-        <f t="shared" ref="M41" si="33">L41*5</f>
+      <c r="M41" s="14">
+        <f>L41*5</f>
         <v>5</v>
       </c>
-      <c r="N41" s="14" t="s">
-        <v>545</v>
-      </c>
-      <c r="O41" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P41" s="49" t="s">
-        <v>509</v>
-      </c>
-      <c r="Q41" s="21">
-        <f t="shared" ref="Q41" si="34">P41*N41</f>
-        <v>0.42200000000000004</v>
-      </c>
-      <c r="R41" s="20"/>
-    </row>
-    <row r="42" spans="1:18" ht="48">
+      <c r="N41" s="14">
+        <v>10</v>
+      </c>
+      <c r="O41" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P41" s="46" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q41" s="15">
+        <f>P41*N41</f>
+        <v>1.61</v>
+      </c>
+      <c r="R41" s="14"/>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42" s="1"/>
       <c r="B42" s="16">
         <f>ROW(B42) - ROW($B$7)</f>
         <v>35</v>
       </c>
-      <c r="C42" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>149</v>
+      <c r="C42" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>144</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="I42" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J42" s="14" t="s">
-        <v>380</v>
-      </c>
-      <c r="K42" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L42" s="14">
+        <v>465</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="I42" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="K42" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L42" s="20">
         <v>1</v>
       </c>
-      <c r="M42" s="14">
-        <f>L42*5</f>
+      <c r="M42" s="20">
+        <f t="shared" ref="M42" si="33">L42*5</f>
         <v>5</v>
       </c>
-      <c r="N42" s="14">
-        <v>10</v>
-      </c>
-      <c r="O42" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P42" s="49" t="s">
-        <v>510</v>
-      </c>
-      <c r="Q42" s="15">
-        <f>P42*N42</f>
-        <v>1.0249999999999999</v>
-      </c>
-      <c r="R42" s="14"/>
+      <c r="N42" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="O42" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P42" s="46" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q42" s="21">
+        <f t="shared" ref="Q42" si="34">P42*N42</f>
+        <v>0.42200000000000004</v>
+      </c>
+      <c r="R42" s="20"/>
     </row>
     <row r="43" spans="1:18" ht="48">
       <c r="A43" s="1"/>
@@ -4690,274 +4774,274 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C43" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="H43" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="I43" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J43" s="20" t="s">
-        <v>381</v>
-      </c>
-      <c r="K43" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L43" s="20">
-        <v>6</v>
-      </c>
-      <c r="M43" s="20">
-        <f t="shared" ref="M43" si="35">L43*5</f>
-        <v>30</v>
-      </c>
-      <c r="N43" s="14" t="s">
-        <v>548</v>
-      </c>
-      <c r="O43" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P43" s="49" t="s">
-        <v>511</v>
-      </c>
-      <c r="Q43" s="21">
-        <f t="shared" ref="Q43" si="36">P43*N43</f>
-        <v>1.0879999999999999</v>
-      </c>
-      <c r="R43" s="20"/>
-    </row>
-    <row r="44" spans="1:18" ht="60">
+      <c r="D43" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="I43" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="K43" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L43" s="14">
+        <v>1</v>
+      </c>
+      <c r="M43" s="14">
+        <f>L43*5</f>
+        <v>5</v>
+      </c>
+      <c r="N43" s="14">
+        <v>10</v>
+      </c>
+      <c r="O43" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P43" s="46" t="s">
+        <v>506</v>
+      </c>
+      <c r="Q43" s="15">
+        <f>P43*N43</f>
+        <v>1.0249999999999999</v>
+      </c>
+      <c r="R43" s="14"/>
+    </row>
+    <row r="44" spans="1:18" ht="48">
       <c r="A44" s="1"/>
       <c r="B44" s="16">
         <f>ROW(B44) - ROW($B$7)</f>
         <v>37</v>
       </c>
-      <c r="C44" s="22" t="s">
-        <v>17</v>
+      <c r="C44" s="23" t="s">
+        <v>14</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="I44" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J44" s="14" t="s">
-        <v>382</v>
-      </c>
-      <c r="K44" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L44" s="14">
-        <v>2</v>
-      </c>
-      <c r="M44" s="14">
-        <f>L44*5</f>
-        <v>10</v>
-      </c>
-      <c r="N44" s="14">
-        <v>15</v>
-      </c>
-      <c r="O44" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P44" s="49" t="s">
-        <v>512</v>
-      </c>
-      <c r="Q44" s="15">
-        <f>P44*N44</f>
-        <v>3.2444999999999999</v>
-      </c>
-      <c r="R44" s="14"/>
-    </row>
-    <row r="45" spans="1:18" ht="24">
+        <v>569</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="H44" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="I44" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="K44" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L44" s="20">
+        <v>7</v>
+      </c>
+      <c r="M44" s="20">
+        <f t="shared" ref="M44" si="35">L44*5</f>
+        <v>35</v>
+      </c>
+      <c r="N44" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="O44" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P44" s="46" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q44" s="21">
+        <f t="shared" ref="Q44" si="36">P44*N44</f>
+        <v>1.0879999999999999</v>
+      </c>
+      <c r="R44" s="20"/>
+    </row>
+    <row r="45" spans="1:18" ht="60">
       <c r="A45" s="1"/>
       <c r="B45" s="17">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C45" s="23" t="s">
-        <v>471</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>152</v>
+      <c r="C45" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="G45" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="H45" s="20" t="s">
-        <v>334</v>
-      </c>
-      <c r="I45" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J45" s="20" t="s">
-        <v>555</v>
-      </c>
-      <c r="K45" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L45" s="20">
-        <v>1</v>
-      </c>
-      <c r="M45" s="20">
-        <f t="shared" ref="M45" si="37">L45*5</f>
-        <v>5</v>
+        <v>465</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="I45" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J45" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="K45" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L45" s="14">
+        <v>2</v>
+      </c>
+      <c r="M45" s="14">
+        <f>L45*5</f>
+        <v>10</v>
       </c>
       <c r="N45" s="14">
-        <v>10</v>
-      </c>
-      <c r="O45" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P45" s="49" t="s">
-        <v>513</v>
-      </c>
-      <c r="Q45" s="21">
-        <f t="shared" ref="Q45" si="38">P45*N45</f>
-        <v>0.97500000000000009</v>
-      </c>
-      <c r="R45" s="20"/>
-    </row>
-    <row r="46" spans="1:18" ht="36">
+        <v>15</v>
+      </c>
+      <c r="O45" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P45" s="46" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q45" s="15">
+        <f>P45*N45</f>
+        <v>3.2444999999999999</v>
+      </c>
+      <c r="R45" s="14"/>
+    </row>
+    <row r="46" spans="1:18" ht="24">
       <c r="A46" s="1"/>
       <c r="B46" s="16">
         <f>ROW(B46) - ROW($B$7)</f>
         <v>39</v>
       </c>
-      <c r="C46" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>153</v>
+      <c r="C46" s="23" t="s">
+        <v>467</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>148</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>335</v>
-      </c>
-      <c r="I46" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J46" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="K46" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L46" s="14">
-        <v>2</v>
-      </c>
-      <c r="M46" s="14">
-        <f>L46*5</f>
+        <v>465</v>
+      </c>
+      <c r="G46" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="H46" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="I46" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J46" s="20" t="s">
+        <v>551</v>
+      </c>
+      <c r="K46" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L46" s="20">
+        <v>1</v>
+      </c>
+      <c r="M46" s="20">
+        <f t="shared" ref="M46" si="37">L46*5</f>
+        <v>5</v>
+      </c>
+      <c r="N46" s="14">
         <v>10</v>
       </c>
-      <c r="N46" s="14">
-        <v>11</v>
-      </c>
-      <c r="O46" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P46" s="49" t="s">
-        <v>514</v>
-      </c>
-      <c r="Q46" s="15">
-        <f>P46*N46</f>
-        <v>12.8161</v>
-      </c>
-      <c r="R46" s="14"/>
-    </row>
-    <row r="47" spans="1:18" ht="24">
+      <c r="O46" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P46" s="46" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q46" s="21">
+        <f t="shared" ref="Q46" si="38">P46*N46</f>
+        <v>0.97500000000000009</v>
+      </c>
+      <c r="R46" s="20"/>
+    </row>
+    <row r="47" spans="1:18" ht="36">
       <c r="A47" s="1"/>
       <c r="B47" s="17">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C47" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>154</v>
+      <c r="C47" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="H47" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="I47" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J47" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="K47" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L47" s="20">
-        <v>8</v>
-      </c>
-      <c r="M47" s="20">
-        <f t="shared" ref="M47" si="39">L47*5</f>
-        <v>40</v>
+        <v>465</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="I47" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="K47" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L47" s="14">
+        <v>2</v>
+      </c>
+      <c r="M47" s="14">
+        <f>L47*5</f>
+        <v>10</v>
       </c>
       <c r="N47" s="14">
-        <v>45</v>
-      </c>
-      <c r="O47" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P47" s="49" t="s">
-        <v>515</v>
-      </c>
-      <c r="Q47" s="21">
-        <f t="shared" ref="Q47" si="40">P47*N47</f>
-        <v>3.1050000000000004</v>
-      </c>
-      <c r="R47" s="20"/>
+        <v>11</v>
+      </c>
+      <c r="O47" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P47" s="46" t="s">
+        <v>510</v>
+      </c>
+      <c r="Q47" s="15">
+        <f>P47*N47</f>
+        <v>12.8161</v>
+      </c>
+      <c r="R47" s="14"/>
     </row>
     <row r="48" spans="1:18" ht="24">
       <c r="A48" s="1"/>
@@ -4965,164 +5049,164 @@
         <f>ROW(B48) - ROW($B$7)</f>
         <v>41</v>
       </c>
-      <c r="C48" s="22" t="s">
+      <c r="C48" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D48" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>155</v>
+      <c r="D48" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>150</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>332</v>
-      </c>
-      <c r="I48" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J48" s="14" t="s">
-        <v>385</v>
-      </c>
-      <c r="K48" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L48" s="14">
-        <v>4</v>
-      </c>
-      <c r="M48" s="14">
-        <f>L48*5</f>
-        <v>20</v>
+        <v>465</v>
+      </c>
+      <c r="G48" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="H48" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="I48" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J48" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="K48" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L48" s="20">
+        <v>8</v>
+      </c>
+      <c r="M48" s="20">
+        <f t="shared" ref="M48" si="39">L48*5</f>
+        <v>40</v>
       </c>
       <c r="N48" s="14">
-        <v>40</v>
-      </c>
-      <c r="O48" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P48" s="49" t="s">
-        <v>516</v>
-      </c>
-      <c r="Q48" s="15">
-        <f>P48*N48</f>
-        <v>1.2759999999999998</v>
-      </c>
-      <c r="R48" s="14"/>
-    </row>
-    <row r="49" spans="1:18" ht="48">
+        <v>45</v>
+      </c>
+      <c r="O48" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P48" s="46" t="s">
+        <v>511</v>
+      </c>
+      <c r="Q48" s="21">
+        <f t="shared" ref="Q48" si="40">P48*N48</f>
+        <v>3.1050000000000004</v>
+      </c>
+      <c r="R48" s="20"/>
+    </row>
+    <row r="49" spans="1:18" ht="24">
       <c r="A49" s="1"/>
       <c r="B49" s="17">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C49" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>156</v>
+      <c r="C49" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>151</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="G49" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="H49" s="20" t="s">
-        <v>336</v>
-      </c>
-      <c r="I49" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J49" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="K49" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L49" s="20">
-        <v>3</v>
-      </c>
-      <c r="M49" s="20">
-        <f t="shared" ref="M49" si="41">L49*5</f>
-        <v>15</v>
+        <v>465</v>
+      </c>
+      <c r="G49" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="I49" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J49" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="K49" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L49" s="14">
+        <v>4</v>
+      </c>
+      <c r="M49" s="14">
+        <f>L49*5</f>
+        <v>20</v>
       </c>
       <c r="N49" s="14">
-        <v>20</v>
-      </c>
-      <c r="O49" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P49" s="49" t="s">
-        <v>517</v>
-      </c>
-      <c r="Q49" s="21">
-        <f t="shared" ref="Q49" si="42">P49*N49</f>
-        <v>4.97</v>
-      </c>
-      <c r="R49" s="20"/>
-    </row>
-    <row r="50" spans="1:18">
+        <v>40</v>
+      </c>
+      <c r="O49" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P49" s="46" t="s">
+        <v>512</v>
+      </c>
+      <c r="Q49" s="15">
+        <f>P49*N49</f>
+        <v>1.2759999999999998</v>
+      </c>
+      <c r="R49" s="14"/>
+    </row>
+    <row r="50" spans="1:18" ht="48">
       <c r="A50" s="1"/>
       <c r="B50" s="16">
         <f>ROW(B50) - ROW($B$7)</f>
         <v>43</v>
       </c>
-      <c r="C50" s="22" t="s">
+      <c r="C50" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="G50" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="H50" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="I50" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J50" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="K50" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L50" s="20">
+        <v>3</v>
+      </c>
+      <c r="M50" s="20">
+        <f t="shared" ref="M50" si="41">L50*5</f>
+        <v>15</v>
+      </c>
+      <c r="N50" s="14">
         <v>20</v>
       </c>
-      <c r="D50" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="F50" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="G50" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="H50" s="14" t="s">
-        <v>337</v>
-      </c>
-      <c r="I50" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J50" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="K50" s="45" t="s">
-        <v>441</v>
-      </c>
-      <c r="L50" s="14">
-        <v>1</v>
-      </c>
-      <c r="M50" s="14">
-        <f>L50*5</f>
-        <v>5</v>
-      </c>
-      <c r="N50" s="14">
-        <v>10</v>
-      </c>
-      <c r="O50" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P50" s="49" t="s">
-        <v>518</v>
-      </c>
-      <c r="Q50" s="15">
-        <f>P50*N50</f>
-        <v>3.5410000000000004</v>
-      </c>
-      <c r="R50" s="14"/>
+      <c r="O50" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P50" s="46" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q50" s="21">
+        <f t="shared" ref="Q50" si="42">P50*N50</f>
+        <v>4.97</v>
+      </c>
+      <c r="R50" s="20"/>
     </row>
     <row r="51" spans="1:18">
       <c r="A51" s="1"/>
@@ -5130,109 +5214,109 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C51" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E51" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="F51" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="G51" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="H51" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="I51" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J51" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="K51" s="46" t="s">
-        <v>468</v>
-      </c>
-      <c r="L51" s="20">
+      <c r="C51" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="G51" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="I51" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J51" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="K51" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="L51" s="14">
         <v>1</v>
       </c>
-      <c r="M51" s="20">
-        <f t="shared" ref="M51" si="43">L51*5</f>
+      <c r="M51" s="14">
+        <f>L51*5</f>
         <v>5</v>
       </c>
-      <c r="N51" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O51" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P51" s="49" t="s">
-        <v>519</v>
-      </c>
-      <c r="Q51" s="21">
-        <f t="shared" ref="Q51" si="44">P51*N51</f>
-        <v>0.33</v>
-      </c>
-      <c r="R51" s="20"/>
-    </row>
-    <row r="52" spans="1:18" ht="24">
+      <c r="N51" s="14">
+        <v>10</v>
+      </c>
+      <c r="O51" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P51" s="46" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q51" s="15">
+        <f>P51*N51</f>
+        <v>3.5410000000000004</v>
+      </c>
+      <c r="R51" s="14"/>
+    </row>
+    <row r="52" spans="1:18">
       <c r="A52" s="1"/>
       <c r="B52" s="16">
         <f>ROW(B52) - ROW($B$7)</f>
         <v>45</v>
       </c>
-      <c r="C52" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="F52" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="G52" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="H52" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="I52" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J52" s="14" t="s">
-        <v>389</v>
-      </c>
-      <c r="K52" s="46" t="s">
-        <v>468</v>
-      </c>
-      <c r="L52" s="14">
-        <v>4</v>
-      </c>
-      <c r="M52" s="14">
-        <f>L52*5</f>
-        <v>20</v>
-      </c>
-      <c r="N52" s="14">
-        <v>40</v>
-      </c>
-      <c r="O52" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P52" s="49" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q52" s="15">
-        <f>P52*N52</f>
-        <v>0.90800000000000003</v>
-      </c>
-      <c r="R52" s="14"/>
+      <c r="C52" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="G52" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="H52" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="I52" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J52" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="K52" s="43" t="s">
+        <v>464</v>
+      </c>
+      <c r="L52" s="20">
+        <v>1</v>
+      </c>
+      <c r="M52" s="20">
+        <f t="shared" ref="M52" si="43">L52*5</f>
+        <v>5</v>
+      </c>
+      <c r="N52" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="O52" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P52" s="46" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q52" s="21">
+        <f t="shared" ref="Q52" si="44">P52*N52</f>
+        <v>0.33</v>
+      </c>
+      <c r="R52" s="20"/>
     </row>
     <row r="53" spans="1:18" ht="24">
       <c r="A53" s="1"/>
@@ -5240,109 +5324,109 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="E53" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="F53" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="G53" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="H53" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="I53" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J53" s="20" t="s">
-        <v>390</v>
-      </c>
-      <c r="K53" s="46" t="s">
-        <v>468</v>
-      </c>
-      <c r="L53" s="20">
-        <v>5</v>
-      </c>
-      <c r="M53" s="20">
-        <f t="shared" ref="M53" si="45">L53*5</f>
-        <v>25</v>
-      </c>
-      <c r="N53" s="14" t="s">
-        <v>548</v>
-      </c>
-      <c r="O53" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P53" s="49" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q53" s="21">
-        <f t="shared" ref="Q53" si="46">P53*N53</f>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="R53" s="20"/>
-    </row>
-    <row r="54" spans="1:18">
+      <c r="D53" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G53" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="H53" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="I53" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J53" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="K53" s="43" t="s">
+        <v>464</v>
+      </c>
+      <c r="L53" s="14">
+        <v>4</v>
+      </c>
+      <c r="M53" s="14">
+        <f>L53*5</f>
+        <v>20</v>
+      </c>
+      <c r="N53" s="14">
+        <v>40</v>
+      </c>
+      <c r="O53" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P53" s="46" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q53" s="15">
+        <f>P53*N53</f>
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="R53" s="14"/>
+    </row>
+    <row r="54" spans="1:18" ht="24">
       <c r="A54" s="1"/>
       <c r="B54" s="16">
         <f>ROW(B54) - ROW($B$7)</f>
         <v>47</v>
       </c>
-      <c r="C54" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E54" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="F54" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="G54" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="H54" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="I54" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J54" s="14" t="s">
-        <v>391</v>
-      </c>
-      <c r="K54" s="45" t="s">
-        <v>442</v>
-      </c>
-      <c r="L54" s="14">
-        <v>1</v>
-      </c>
-      <c r="M54" s="14">
-        <f>L54*5</f>
+      <c r="C54" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="G54" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="H54" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="I54" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J54" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="K54" s="43" t="s">
+        <v>464</v>
+      </c>
+      <c r="L54" s="20">
         <v>5</v>
+      </c>
+      <c r="M54" s="20">
+        <f t="shared" ref="M54" si="45">L54*5</f>
+        <v>25</v>
       </c>
       <c r="N54" s="14" t="s">
         <v>544</v>
       </c>
-      <c r="O54" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P54" s="49" t="s">
-        <v>499</v>
-      </c>
-      <c r="Q54" s="15">
-        <f>P54*N54</f>
-        <v>0.54800000000000004</v>
-      </c>
-      <c r="R54" s="14"/>
+      <c r="O54" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P54" s="46" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q54" s="21">
+        <f t="shared" ref="Q54" si="46">P54*N54</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="R54" s="20"/>
     </row>
     <row r="55" spans="1:18">
       <c r="A55" s="1"/>
@@ -5350,54 +5434,54 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C55" s="23" t="s">
+      <c r="C55" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D55" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="F55" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="G55" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="H55" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I55" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J55" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="K55" s="46" t="s">
-        <v>443</v>
-      </c>
-      <c r="L55" s="20">
+      <c r="D55" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="H55" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="I55" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J55" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="K55" s="42" t="s">
+        <v>438</v>
+      </c>
+      <c r="L55" s="14">
         <v>1</v>
       </c>
-      <c r="M55" s="20">
-        <f t="shared" ref="M55" si="47">L55*5</f>
+      <c r="M55" s="14">
+        <f>L55*5</f>
         <v>5</v>
       </c>
       <c r="N55" s="14" t="s">
-        <v>547</v>
-      </c>
-      <c r="O55" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P55" s="49" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q55" s="21">
-        <f t="shared" ref="Q55" si="48">P55*N55</f>
-        <v>1.01</v>
-      </c>
-      <c r="R55" s="20"/>
+        <v>540</v>
+      </c>
+      <c r="O55" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P55" s="46" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q55" s="15">
+        <f>P55*N55</f>
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="R55" s="14"/>
     </row>
     <row r="56" spans="1:18">
       <c r="A56" s="1"/>
@@ -5405,54 +5489,54 @@
         <f>ROW(B56) - ROW($B$7)</f>
         <v>49</v>
       </c>
-      <c r="C56" s="22" t="s">
+      <c r="C56" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D56" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E56" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F56" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="G56" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="H56" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="I56" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J56" s="14" t="s">
-        <v>393</v>
-      </c>
-      <c r="K56" s="45" t="s">
-        <v>444</v>
-      </c>
-      <c r="L56" s="14">
+      <c r="D56" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="F56" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G56" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="H56" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="I56" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J56" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="K56" s="43" t="s">
+        <v>439</v>
+      </c>
+      <c r="L56" s="20">
         <v>1</v>
       </c>
-      <c r="M56" s="14">
-        <f>L56*5</f>
+      <c r="M56" s="20">
+        <f t="shared" ref="M56" si="47">L56*5</f>
         <v>5</v>
       </c>
       <c r="N56" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O56" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P56" s="49" t="s">
-        <v>523</v>
-      </c>
-      <c r="Q56" s="15">
-        <f>P56*N56</f>
-        <v>0.06</v>
-      </c>
-      <c r="R56" s="14"/>
+        <v>543</v>
+      </c>
+      <c r="O56" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P56" s="46" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q56" s="21">
+        <f t="shared" ref="Q56" si="48">P56*N56</f>
+        <v>1.01</v>
+      </c>
+      <c r="R56" s="20"/>
     </row>
     <row r="57" spans="1:18">
       <c r="A57" s="1"/>
@@ -5460,54 +5544,54 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E57" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="F57" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="G57" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="H57" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I57" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J57" s="20" t="s">
-        <v>394</v>
-      </c>
-      <c r="K57" s="46" t="s">
-        <v>445</v>
-      </c>
-      <c r="L57" s="20">
+      <c r="D57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="F57" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="H57" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="I57" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J57" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="K57" s="42" t="s">
+        <v>440</v>
+      </c>
+      <c r="L57" s="14">
         <v>1</v>
       </c>
-      <c r="M57" s="20">
-        <f t="shared" ref="M57" si="49">L57*5</f>
+      <c r="M57" s="14">
+        <f>L57*5</f>
         <v>5</v>
       </c>
       <c r="N57" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O57" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P57" s="49" t="s">
-        <v>524</v>
-      </c>
-      <c r="Q57" s="21">
-        <f t="shared" ref="Q57" si="50">P57*N57</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R57" s="20"/>
+        <v>542</v>
+      </c>
+      <c r="O57" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P57" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q57" s="15">
+        <f>P57*N57</f>
+        <v>0.06</v>
+      </c>
+      <c r="R57" s="14"/>
     </row>
     <row r="58" spans="1:18">
       <c r="A58" s="1"/>
@@ -5518,53 +5602,53 @@
       <c r="C58" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D58" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E58" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="F58" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="G58" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="H58" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="I58" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J58" s="14" t="s">
-        <v>395</v>
-      </c>
-      <c r="K58" s="45" t="s">
-        <v>446</v>
-      </c>
-      <c r="L58" s="14">
+      <c r="D58" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G58" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="H58" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="I58" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J58" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="K58" s="43" t="s">
+        <v>441</v>
+      </c>
+      <c r="L58" s="20">
         <v>1</v>
       </c>
-      <c r="M58" s="14">
-        <f>L58*5</f>
+      <c r="M58" s="20">
+        <f t="shared" ref="M58" si="49">L58*5</f>
         <v>5</v>
       </c>
       <c r="N58" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O58" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P58" s="49" t="s">
-        <v>524</v>
-      </c>
-      <c r="Q58" s="15">
-        <f>P58*N58</f>
+        <v>542</v>
+      </c>
+      <c r="O58" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P58" s="46" t="s">
+        <v>520</v>
+      </c>
+      <c r="Q58" s="21">
+        <f t="shared" ref="Q58" si="50">P58*N58</f>
         <v>6.9999999999999993E-2</v>
       </c>
-      <c r="R58" s="14"/>
-    </row>
-    <row r="59" spans="1:18" ht="48">
+      <c r="R58" s="20"/>
+    </row>
+    <row r="59" spans="1:18">
       <c r="A59" s="1"/>
       <c r="B59" s="17">
         <f t="shared" si="0"/>
@@ -5573,53 +5657,53 @@
       <c r="C59" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D59" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E59" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="F59" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="G59" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="H59" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I59" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J59" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="K59" s="46" t="s">
-        <v>447</v>
-      </c>
-      <c r="L59" s="20">
-        <v>23</v>
-      </c>
-      <c r="M59" s="20">
-        <f t="shared" ref="M59" si="51">L59*5</f>
-        <v>115</v>
+      <c r="D59" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="F59" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G59" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="H59" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="I59" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J59" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="K59" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="L59" s="14">
+        <v>1</v>
+      </c>
+      <c r="M59" s="14">
+        <f>L59*5</f>
+        <v>5</v>
       </c>
       <c r="N59" s="14" t="s">
-        <v>549</v>
-      </c>
-      <c r="O59" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P59" s="49" t="s">
-        <v>525</v>
-      </c>
-      <c r="Q59" s="21">
-        <f t="shared" ref="Q59" si="52">P59*N59</f>
-        <v>0.1</v>
-      </c>
-      <c r="R59" s="20"/>
-    </row>
-    <row r="60" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="O59" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P59" s="46" t="s">
+        <v>520</v>
+      </c>
+      <c r="Q59" s="15">
+        <f>P59*N59</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R59" s="14"/>
+    </row>
+    <row r="60" spans="1:18" ht="48">
       <c r="A60" s="1"/>
       <c r="B60" s="16">
         <f>ROW(B60) - ROW($B$7)</f>
@@ -5628,52 +5712,51 @@
       <c r="C60" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D60" s="48" t="s">
-        <v>81</v>
-      </c>
-      <c r="E60" s="48" t="s">
-        <v>167</v>
-      </c>
-      <c r="F60" s="48" t="s">
-        <v>224</v>
-      </c>
-      <c r="G60" s="48" t="s">
-        <v>286</v>
-      </c>
-      <c r="H60" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="I60" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J60" s="48" t="s">
-        <v>397</v>
-      </c>
-      <c r="K60" s="47" t="s">
-        <v>433</v>
-      </c>
-      <c r="L60" s="48">
-        <v>2</v>
-      </c>
-      <c r="M60" s="48">
-        <f>L60*5</f>
-        <v>10</v>
-      </c>
-      <c r="N60" s="48" t="s">
-        <v>468</v>
-      </c>
-      <c r="O60" s="52" t="s">
-        <v>478</v>
-      </c>
-      <c r="P60" s="53" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q60" s="54" t="s">
-        <v>468</v>
-      </c>
-      <c r="R60" s="51" t="s">
-        <v>560</v>
-      </c>
+      <c r="D60" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F60" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G60" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="H60" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="I60" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J60" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="K60" s="43" t="s">
+        <v>443</v>
+      </c>
+      <c r="L60" s="20">
+        <v>23</v>
+      </c>
+      <c r="M60" s="20">
+        <f t="shared" ref="M60" si="51">L60*5</f>
+        <v>115</v>
+      </c>
+      <c r="N60" s="14" t="s">
+        <v>545</v>
+      </c>
+      <c r="O60" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P60" s="46" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q60" s="21">
+        <f t="shared" ref="Q60" si="52">P60*N60</f>
+        <v>0.1</v>
+      </c>
+      <c r="R60" s="20"/>
     </row>
     <row r="61" spans="1:18">
       <c r="A61" s="1"/>
@@ -5684,53 +5767,54 @@
       <c r="C61" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D61" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E61" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="F61" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="G61" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="H61" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I61" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J61" s="20" t="s">
-        <v>397</v>
-      </c>
-      <c r="K61" s="46" t="s">
-        <v>448</v>
-      </c>
-      <c r="L61" s="20">
+      <c r="D61" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="E61" s="45" t="s">
+        <v>163</v>
+      </c>
+      <c r="F61" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="G61" s="45" t="s">
+        <v>282</v>
+      </c>
+      <c r="H61" s="45" t="s">
+        <v>312</v>
+      </c>
+      <c r="I61" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J61" s="45" t="s">
+        <v>393</v>
+      </c>
+      <c r="K61" s="44" t="s">
+        <v>429</v>
+      </c>
+      <c r="L61" s="45">
         <v>2</v>
       </c>
-      <c r="M61" s="20">
-        <f t="shared" ref="M61" si="53">L61*5</f>
+      <c r="M61" s="45">
+        <f>L61*5</f>
         <v>10</v>
       </c>
-      <c r="N61" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O61" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P61" s="49" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q61" s="21">
-        <f t="shared" ref="Q61" si="54">P61*N61</f>
-        <v>0.1</v>
-      </c>
-      <c r="R61" s="20"/>
-    </row>
-    <row r="62" spans="1:18" ht="24">
+      <c r="N61" s="45" t="s">
+        <v>464</v>
+      </c>
+      <c r="O61" s="49" t="s">
+        <v>474</v>
+      </c>
+      <c r="P61" s="50" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q61" s="51" t="s">
+        <v>464</v>
+      </c>
+      <c r="R61" s="48" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18">
       <c r="A62" s="1"/>
       <c r="B62" s="16">
         <f>ROW(B62) - ROW($B$7)</f>
@@ -5739,53 +5823,53 @@
       <c r="C62" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D62" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E62" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="F62" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="G62" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="H62" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="I62" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J62" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="K62" s="45" t="s">
-        <v>449</v>
-      </c>
-      <c r="L62" s="14">
-        <v>12</v>
-      </c>
-      <c r="M62" s="14">
-        <f>L62*5</f>
-        <v>60</v>
+      <c r="D62" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="F62" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="G62" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="H62" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="I62" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J62" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="K62" s="43" t="s">
+        <v>444</v>
+      </c>
+      <c r="L62" s="20">
+        <v>2</v>
+      </c>
+      <c r="M62" s="20">
+        <f t="shared" ref="M62" si="53">L62*5</f>
+        <v>10</v>
       </c>
       <c r="N62" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O62" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P62" s="49" t="s">
-        <v>526</v>
-      </c>
-      <c r="Q62" s="15">
-        <f>P62*N62</f>
-        <v>0.12</v>
-      </c>
-      <c r="R62" s="14"/>
-    </row>
-    <row r="63" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="O62" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P62" s="46" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q62" s="21">
+        <f t="shared" ref="Q62" si="54">P62*N62</f>
+        <v>0.1</v>
+      </c>
+      <c r="R62" s="20"/>
+    </row>
+    <row r="63" spans="1:18" ht="24">
       <c r="A63" s="1"/>
       <c r="B63" s="17">
         <f t="shared" si="0"/>
@@ -5794,53 +5878,53 @@
       <c r="C63" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D63" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E63" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="F63" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="G63" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="H63" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I63" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J63" s="20" t="s">
-        <v>399</v>
-      </c>
-      <c r="K63" s="46" t="s">
-        <v>450</v>
-      </c>
-      <c r="L63" s="20">
-        <v>1</v>
-      </c>
-      <c r="M63" s="20">
-        <f t="shared" ref="M63" si="55">L63*5</f>
-        <v>5</v>
+      <c r="D63" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="F63" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="G63" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="H63" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="I63" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J63" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="K63" s="42" t="s">
+        <v>445</v>
+      </c>
+      <c r="L63" s="14">
+        <v>12</v>
+      </c>
+      <c r="M63" s="14">
+        <f>L63*5</f>
+        <v>60</v>
       </c>
       <c r="N63" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O63" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P63" s="49" t="s">
-        <v>527</v>
-      </c>
-      <c r="Q63" s="21">
-        <f t="shared" ref="Q63" si="56">P63*N63</f>
-        <v>0.26</v>
-      </c>
-      <c r="R63" s="20"/>
-    </row>
-    <row r="64" spans="1:18" ht="36">
+        <v>542</v>
+      </c>
+      <c r="O63" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P63" s="46" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q63" s="15">
+        <f>P63*N63</f>
+        <v>0.12</v>
+      </c>
+      <c r="R63" s="14"/>
+    </row>
+    <row r="64" spans="1:18">
       <c r="A64" s="1"/>
       <c r="B64" s="16">
         <f>ROW(B64) - ROW($B$7)</f>
@@ -5849,53 +5933,53 @@
       <c r="C64" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D64" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="E64" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="F64" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="G64" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="H64" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="I64" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J64" s="14" t="s">
-        <v>559</v>
-      </c>
-      <c r="K64" s="45" t="s">
-        <v>451</v>
-      </c>
-      <c r="L64" s="14">
-        <v>17</v>
-      </c>
-      <c r="M64" s="14">
-        <f>L64*5</f>
-        <v>85</v>
-      </c>
-      <c r="N64" s="14">
-        <v>100</v>
-      </c>
-      <c r="O64" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P64" s="49">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q64" s="15">
-        <f>P64*N64</f>
-        <v>0.12</v>
-      </c>
-      <c r="R64" s="14"/>
-    </row>
-    <row r="65" spans="1:18">
+      <c r="D64" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F64" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G64" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="H64" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="I64" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J64" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="K64" s="43" t="s">
+        <v>446</v>
+      </c>
+      <c r="L64" s="20">
+        <v>1</v>
+      </c>
+      <c r="M64" s="20">
+        <f t="shared" ref="M64" si="55">L64*5</f>
+        <v>5</v>
+      </c>
+      <c r="N64" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="O64" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P64" s="46" t="s">
+        <v>523</v>
+      </c>
+      <c r="Q64" s="21">
+        <f t="shared" ref="Q64" si="56">P64*N64</f>
+        <v>0.26</v>
+      </c>
+      <c r="R64" s="20"/>
+    </row>
+    <row r="65" spans="1:18" ht="36">
       <c r="A65" s="1"/>
       <c r="B65" s="17">
         <f t="shared" si="0"/>
@@ -5905,52 +5989,52 @@
         <v>22</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="E65" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="F65" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="G65" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="H65" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I65" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J65" s="20" t="s">
-        <v>401</v>
-      </c>
-      <c r="K65" s="46" t="s">
-        <v>452</v>
-      </c>
-      <c r="L65" s="20">
-        <v>2</v>
-      </c>
-      <c r="M65" s="20">
-        <f t="shared" ref="M65" si="57">L65*5</f>
-        <v>10</v>
-      </c>
-      <c r="N65" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O65" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P65" s="49" t="s">
-        <v>524</v>
-      </c>
-      <c r="Q65" s="21">
-        <f t="shared" ref="Q65" si="58">P65*N65</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R65" s="20"/>
-    </row>
-    <row r="66" spans="1:18" ht="24">
+        <v>570</v>
+      </c>
+      <c r="E65" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="F65" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G65" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="H65" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="I65" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J65" s="14" t="s">
+        <v>555</v>
+      </c>
+      <c r="K65" s="42" t="s">
+        <v>447</v>
+      </c>
+      <c r="L65" s="14">
+        <v>18</v>
+      </c>
+      <c r="M65" s="14">
+        <f>L65*5</f>
+        <v>90</v>
+      </c>
+      <c r="N65" s="14">
+        <v>100</v>
+      </c>
+      <c r="O65" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P65" s="46">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q65" s="15">
+        <f>P65*N65</f>
+        <v>0.12</v>
+      </c>
+      <c r="R65" s="14"/>
+    </row>
+    <row r="66" spans="1:18">
       <c r="A66" s="1"/>
       <c r="B66" s="16">
         <f>ROW(B66) - ROW($B$7)</f>
@@ -5959,53 +6043,53 @@
       <c r="C66" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E66" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="F66" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="G66" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="H66" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="I66" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J66" s="14" t="s">
-        <v>556</v>
-      </c>
-      <c r="K66" s="45" t="s">
-        <v>453</v>
-      </c>
-      <c r="L66" s="14">
-        <v>8</v>
-      </c>
-      <c r="M66" s="14">
-        <f>L66*5</f>
-        <v>40</v>
+      <c r="D66" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="F66" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G66" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="H66" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="I66" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J66" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="K66" s="43" t="s">
+        <v>448</v>
+      </c>
+      <c r="L66" s="20">
+        <v>2</v>
+      </c>
+      <c r="M66" s="20">
+        <f t="shared" ref="M66" si="57">L66*5</f>
+        <v>10</v>
       </c>
       <c r="N66" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O66" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P66" s="49" t="s">
-        <v>523</v>
-      </c>
-      <c r="Q66" s="15">
-        <f>P66*N66</f>
-        <v>0.06</v>
-      </c>
-      <c r="R66" s="14"/>
-    </row>
-    <row r="67" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="O66" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P66" s="46" t="s">
+        <v>520</v>
+      </c>
+      <c r="Q66" s="21">
+        <f t="shared" ref="Q66" si="58">P66*N66</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R66" s="20"/>
+    </row>
+    <row r="67" spans="1:18" ht="24">
       <c r="A67" s="1"/>
       <c r="B67" s="17">
         <f t="shared" si="0"/>
@@ -6014,51 +6098,51 @@
       <c r="C67" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D67" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E67" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="F67" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="G67" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="H67" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I67" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J67" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="K67" s="46" t="s">
-        <v>454</v>
-      </c>
-      <c r="L67" s="20">
-        <v>2</v>
-      </c>
-      <c r="M67" s="20">
-        <f t="shared" ref="M67" si="59">L67*5</f>
-        <v>10</v>
+      <c r="D67" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E67" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="F67" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="H67" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="I67" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J67" s="14" t="s">
+        <v>552</v>
+      </c>
+      <c r="K67" s="42" t="s">
+        <v>449</v>
+      </c>
+      <c r="L67" s="14">
+        <v>8</v>
+      </c>
+      <c r="M67" s="14">
+        <f>L67*5</f>
+        <v>40</v>
       </c>
       <c r="N67" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O67" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P67" s="49" t="s">
-        <v>523</v>
-      </c>
-      <c r="Q67" s="21">
-        <f t="shared" ref="Q67" si="60">P67*N67</f>
+        <v>542</v>
+      </c>
+      <c r="O67" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P67" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q67" s="15">
+        <f>P67*N67</f>
         <v>0.06</v>
       </c>
-      <c r="R67" s="20"/>
+      <c r="R67" s="14"/>
     </row>
     <row r="68" spans="1:18">
       <c r="A68" s="1"/>
@@ -6069,53 +6153,53 @@
       <c r="C68" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D68" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E68" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="F68" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="G68" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="H68" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="I68" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J68" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="K68" s="45" t="s">
-        <v>455</v>
-      </c>
-      <c r="L68" s="14">
+      <c r="D68" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E68" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F68" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G68" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="H68" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="I68" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J68" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="K68" s="43" t="s">
+        <v>450</v>
+      </c>
+      <c r="L68" s="20">
         <v>2</v>
       </c>
-      <c r="M68" s="14">
-        <f>L68*5</f>
+      <c r="M68" s="20">
+        <f t="shared" ref="M68" si="59">L68*5</f>
         <v>10</v>
       </c>
       <c r="N68" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O68" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P68" s="49" t="s">
-        <v>524</v>
-      </c>
-      <c r="Q68" s="15">
-        <f>P68*N68</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R68" s="14"/>
-    </row>
-    <row r="69" spans="1:18" ht="24">
+        <v>542</v>
+      </c>
+      <c r="O68" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P68" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q68" s="21">
+        <f t="shared" ref="Q68" si="60">P68*N68</f>
+        <v>0.06</v>
+      </c>
+      <c r="R68" s="20"/>
+    </row>
+    <row r="69" spans="1:18">
       <c r="A69" s="1"/>
       <c r="B69" s="17">
         <f t="shared" si="0"/>
@@ -6124,53 +6208,53 @@
       <c r="C69" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D69" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E69" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="F69" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="G69" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="H69" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I69" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J69" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="K69" s="46" t="s">
-        <v>448</v>
-      </c>
-      <c r="L69" s="20">
-        <v>14</v>
-      </c>
-      <c r="M69" s="20">
-        <f t="shared" ref="M69" si="61">L69*5</f>
-        <v>70</v>
+      <c r="D69" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E69" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="F69" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G69" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="H69" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="I69" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J69" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="K69" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="L69" s="14">
+        <v>2</v>
+      </c>
+      <c r="M69" s="14">
+        <f>L69*5</f>
+        <v>10</v>
       </c>
       <c r="N69" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O69" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P69" s="49" t="s">
-        <v>523</v>
-      </c>
-      <c r="Q69" s="21">
-        <f t="shared" ref="Q69" si="62">P69*N69</f>
-        <v>0.06</v>
-      </c>
-      <c r="R69" s="20"/>
-    </row>
-    <row r="70" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="O69" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P69" s="46" t="s">
+        <v>520</v>
+      </c>
+      <c r="Q69" s="15">
+        <f>P69*N69</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R69" s="14"/>
+    </row>
+    <row r="70" spans="1:18" ht="24">
       <c r="A70" s="1"/>
       <c r="B70" s="16">
         <f>ROW(B70) - ROW($B$7)</f>
@@ -6179,51 +6263,51 @@
       <c r="C70" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D70" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E70" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="F70" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="G70" s="48" t="s">
-        <v>295</v>
+      <c r="D70" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E70" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F70" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G70" s="20" t="s">
+        <v>290</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I70" s="55" t="s">
-        <v>562</v>
-      </c>
-      <c r="J70" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="K70" s="45" t="s">
-        <v>456</v>
-      </c>
-      <c r="L70" s="14">
-        <v>4</v>
-      </c>
-      <c r="M70" s="14">
-        <f>L70*5</f>
-        <v>20</v>
+        <v>312</v>
+      </c>
+      <c r="I70" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J70" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="K70" s="43" t="s">
+        <v>444</v>
+      </c>
+      <c r="L70" s="20">
+        <v>14</v>
+      </c>
+      <c r="M70" s="20">
+        <f t="shared" ref="M70" si="61">L70*5</f>
+        <v>70</v>
       </c>
       <c r="N70" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O70" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P70" s="49" t="s">
-        <v>523</v>
-      </c>
-      <c r="Q70" s="15">
-        <f>P70*N70</f>
+        <v>542</v>
+      </c>
+      <c r="O70" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P70" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q70" s="21">
+        <f t="shared" ref="Q70" si="62">P70*N70</f>
         <v>0.06</v>
       </c>
-      <c r="R70" s="14"/>
+      <c r="R70" s="20"/>
     </row>
     <row r="71" spans="1:18">
       <c r="A71" s="1"/>
@@ -6234,51 +6318,51 @@
       <c r="C71" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D71" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="E71" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="F71" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="G71" s="20" t="s">
-        <v>296</v>
+      <c r="D71" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E71" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="F71" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="G71" s="45" t="s">
+        <v>291</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I71" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J71" s="20" t="s">
-        <v>406</v>
-      </c>
-      <c r="K71" s="46" t="s">
-        <v>457</v>
-      </c>
-      <c r="L71" s="20">
-        <v>2</v>
-      </c>
-      <c r="M71" s="20">
-        <f t="shared" ref="M71" si="63">L71*5</f>
-        <v>10</v>
+        <v>312</v>
+      </c>
+      <c r="I71" s="52" t="s">
+        <v>558</v>
+      </c>
+      <c r="J71" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="K71" s="42" t="s">
+        <v>452</v>
+      </c>
+      <c r="L71" s="14">
+        <v>4</v>
+      </c>
+      <c r="M71" s="14">
+        <f>L71*5</f>
+        <v>20</v>
       </c>
       <c r="N71" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O71" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P71" s="49" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q71" s="21">
-        <f t="shared" ref="Q71" si="64">P71*N71</f>
-        <v>0.1</v>
-      </c>
-      <c r="R71" s="20"/>
+        <v>542</v>
+      </c>
+      <c r="O71" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P71" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q71" s="15">
+        <f>P71*N71</f>
+        <v>0.06</v>
+      </c>
+      <c r="R71" s="14"/>
     </row>
     <row r="72" spans="1:18">
       <c r="A72" s="1"/>
@@ -6286,54 +6370,54 @@
         <f>ROW(B72) - ROW($B$7)</f>
         <v>65</v>
       </c>
-      <c r="C72" s="22" t="s">
+      <c r="C72" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D72" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="F72" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="G72" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="H72" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="I72" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J72" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="K72" s="45" t="s">
-        <v>458</v>
-      </c>
-      <c r="L72" s="14">
-        <v>6</v>
-      </c>
-      <c r="M72" s="14">
-        <f>L72*5</f>
-        <v>30</v>
+      <c r="D72" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F72" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="G72" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="H72" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="I72" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J72" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="K72" s="43" t="s">
+        <v>453</v>
+      </c>
+      <c r="L72" s="20">
+        <v>2</v>
+      </c>
+      <c r="M72" s="20">
+        <f t="shared" ref="M72" si="63">L72*5</f>
+        <v>10</v>
       </c>
       <c r="N72" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O72" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P72" s="49" t="s">
-        <v>528</v>
-      </c>
-      <c r="Q72" s="15">
-        <f>P72*N72</f>
-        <v>0.09</v>
-      </c>
-      <c r="R72" s="14"/>
+        <v>542</v>
+      </c>
+      <c r="O72" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P72" s="46" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q72" s="21">
+        <f t="shared" ref="Q72" si="64">P72*N72</f>
+        <v>0.1</v>
+      </c>
+      <c r="R72" s="20"/>
     </row>
     <row r="73" spans="1:18">
       <c r="A73" s="1"/>
@@ -6341,55 +6425,54 @@
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C73" s="23" t="s">
+      <c r="C73" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="E73" s="48" t="s">
-        <v>170</v>
-      </c>
-      <c r="F73" s="48" t="s">
-        <v>223</v>
-      </c>
-      <c r="G73" s="48" t="s">
-        <v>289</v>
-      </c>
-      <c r="H73" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="I73" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J73" s="48" t="s">
-        <v>400</v>
-      </c>
-      <c r="K73" s="47" t="s">
-        <v>433</v>
-      </c>
-      <c r="L73" s="48">
-        <v>1</v>
-      </c>
-      <c r="M73" s="48">
-        <f t="shared" ref="M73" si="65">L73*5</f>
-        <v>5</v>
-      </c>
-      <c r="N73" s="48" t="s">
-        <v>468</v>
-      </c>
-      <c r="O73" s="52" t="s">
-        <v>478</v>
-      </c>
-      <c r="P73" s="53" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q73" s="54" t="s">
-        <v>468</v>
-      </c>
-      <c r="R73" s="51" t="s">
-        <v>560</v>
-      </c>
+      <c r="D73" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E73" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="F73" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="G73" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="H73" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="I73" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J73" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="K73" s="42" t="s">
+        <v>454</v>
+      </c>
+      <c r="L73" s="14">
+        <v>6</v>
+      </c>
+      <c r="M73" s="14">
+        <f>L73*5</f>
+        <v>30</v>
+      </c>
+      <c r="N73" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="O73" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P73" s="46" t="s">
+        <v>524</v>
+      </c>
+      <c r="Q73" s="15">
+        <f>P73*N73</f>
+        <v>0.09</v>
+      </c>
+      <c r="R73" s="14"/>
     </row>
     <row r="74" spans="1:18">
       <c r="A74" s="1"/>
@@ -6397,54 +6480,55 @@
         <f>ROW(B74) - ROW($B$7)</f>
         <v>67</v>
       </c>
-      <c r="C74" s="22" t="s">
+      <c r="C74" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D74" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E74" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="F74" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="G74" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H74" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="I74" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J74" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="K74" s="45" t="s">
-        <v>459</v>
-      </c>
-      <c r="L74" s="14">
+      <c r="D74" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="E74" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="F74" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="G74" s="45" t="s">
+        <v>285</v>
+      </c>
+      <c r="H74" s="45" t="s">
+        <v>312</v>
+      </c>
+      <c r="I74" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J74" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="K74" s="44" t="s">
+        <v>429</v>
+      </c>
+      <c r="L74" s="45">
         <v>1</v>
       </c>
-      <c r="M74" s="14">
-        <f>L74*5</f>
+      <c r="M74" s="45">
+        <f t="shared" ref="M74" si="65">L74*5</f>
         <v>5</v>
       </c>
-      <c r="N74" s="14" t="s">
-        <v>547</v>
-      </c>
-      <c r="O74" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P74" s="49" t="s">
-        <v>529</v>
-      </c>
-      <c r="Q74" s="15">
-        <f>P74*N74</f>
-        <v>1.02</v>
-      </c>
-      <c r="R74" s="14"/>
+      <c r="N74" s="45" t="s">
+        <v>464</v>
+      </c>
+      <c r="O74" s="49" t="s">
+        <v>474</v>
+      </c>
+      <c r="P74" s="50" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q74" s="51" t="s">
+        <v>464</v>
+      </c>
+      <c r="R74" s="48" t="s">
+        <v>556</v>
+      </c>
     </row>
     <row r="75" spans="1:18">
       <c r="A75" s="1"/>
@@ -6452,54 +6536,54 @@
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D75" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="E75" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="F75" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="G75" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="H75" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I75" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J75" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="K75" s="46" t="s">
-        <v>447</v>
-      </c>
-      <c r="L75" s="20">
+      <c r="D75" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E75" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="F75" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G75" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="H75" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="I75" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J75" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="K75" s="42" t="s">
+        <v>455</v>
+      </c>
+      <c r="L75" s="14">
         <v>1</v>
       </c>
-      <c r="M75" s="20">
-        <f t="shared" ref="M75" si="66">L75*5</f>
+      <c r="M75" s="14">
+        <f>L75*5</f>
         <v>5</v>
       </c>
       <c r="N75" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O75" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P75" s="49" t="s">
-        <v>528</v>
-      </c>
-      <c r="Q75" s="21">
-        <f t="shared" ref="Q75" si="67">P75*N75</f>
-        <v>0.09</v>
-      </c>
-      <c r="R75" s="20"/>
+        <v>543</v>
+      </c>
+      <c r="O75" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P75" s="46" t="s">
+        <v>525</v>
+      </c>
+      <c r="Q75" s="15">
+        <f>P75*N75</f>
+        <v>1.02</v>
+      </c>
+      <c r="R75" s="14"/>
     </row>
     <row r="76" spans="1:18">
       <c r="A76" s="1"/>
@@ -6507,54 +6591,54 @@
         <f>ROW(B76) - ROW($B$7)</f>
         <v>69</v>
       </c>
-      <c r="C76" s="22" t="s">
+      <c r="C76" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D76" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E76" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="F76" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="G76" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="H76" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="I76" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J76" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="K76" s="45" t="s">
-        <v>448</v>
-      </c>
-      <c r="L76" s="14">
-        <v>2</v>
-      </c>
-      <c r="M76" s="14">
-        <f>L76*5</f>
-        <v>10</v>
+      <c r="D76" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="F76" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="G76" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="H76" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="I76" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J76" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="K76" s="43" t="s">
+        <v>443</v>
+      </c>
+      <c r="L76" s="20">
+        <v>1</v>
+      </c>
+      <c r="M76" s="20">
+        <f t="shared" ref="M76" si="66">L76*5</f>
+        <v>5</v>
       </c>
       <c r="N76" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O76" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P76" s="49" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q76" s="15">
-        <f>P76*N76</f>
-        <v>0.1</v>
-      </c>
-      <c r="R76" s="14"/>
+        <v>542</v>
+      </c>
+      <c r="O76" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P76" s="46" t="s">
+        <v>524</v>
+      </c>
+      <c r="Q76" s="21">
+        <f t="shared" ref="Q76" si="67">P76*N76</f>
+        <v>0.09</v>
+      </c>
+      <c r="R76" s="20"/>
     </row>
     <row r="77" spans="1:18">
       <c r="A77" s="1"/>
@@ -6562,54 +6646,54 @@
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C77" s="23" t="s">
+      <c r="C77" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D77" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E77" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="F77" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="G77" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="H77" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="I77" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J77" s="20" t="s">
-        <v>411</v>
-      </c>
-      <c r="K77" s="46" t="s">
-        <v>460</v>
-      </c>
-      <c r="L77" s="20">
-        <v>4</v>
-      </c>
-      <c r="M77" s="20">
-        <f t="shared" ref="M77" si="68">L77*5</f>
-        <v>20</v>
+      <c r="D77" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E77" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="F77" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G77" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="I77" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J77" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="K77" s="42" t="s">
+        <v>444</v>
+      </c>
+      <c r="L77" s="14">
+        <v>2</v>
+      </c>
+      <c r="M77" s="14">
+        <f>L77*5</f>
+        <v>10</v>
       </c>
       <c r="N77" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="O77" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P77" s="49" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q77" s="21">
-        <f t="shared" ref="Q77" si="69">P77*N77</f>
+        <v>542</v>
+      </c>
+      <c r="O77" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P77" s="46" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q77" s="15">
+        <f>P77*N77</f>
         <v>0.1</v>
       </c>
-      <c r="R77" s="20"/>
+      <c r="R77" s="14"/>
     </row>
     <row r="78" spans="1:18">
       <c r="A78" s="1"/>
@@ -6617,884 +6701,1265 @@
         <f>ROW(B78) - ROW($B$7)</f>
         <v>71</v>
       </c>
-      <c r="C78" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D78" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E78" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="F78" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="G78" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="H78" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="I78" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J78" s="14" t="s">
-        <v>412</v>
-      </c>
-      <c r="K78" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L78" s="14">
-        <v>2</v>
-      </c>
-      <c r="M78" s="14">
-        <f>L78*5</f>
-        <v>10</v>
-      </c>
-      <c r="N78" s="14">
-        <v>15</v>
-      </c>
-      <c r="O78" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P78" s="49" t="s">
-        <v>530</v>
-      </c>
-      <c r="Q78" s="15">
-        <f>P78*N78</f>
-        <v>2.3280000000000003</v>
-      </c>
-      <c r="R78" s="14"/>
-    </row>
-    <row r="79" spans="1:18" ht="36">
+      <c r="C78" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D78" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="E78" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F78" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="G78" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="H78" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="I78" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J78" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="K78" s="43" t="s">
+        <v>456</v>
+      </c>
+      <c r="L78" s="20">
+        <v>4</v>
+      </c>
+      <c r="M78" s="20">
+        <f t="shared" ref="M78:M79" si="68">L78*5</f>
+        <v>20</v>
+      </c>
+      <c r="N78" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="O78" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P78" s="46" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q78" s="21">
+        <f t="shared" ref="Q78" si="69">P78*N78</f>
+        <v>0.1</v>
+      </c>
+      <c r="R78" s="20"/>
+    </row>
+    <row r="79" spans="1:18">
       <c r="A79" s="1"/>
-      <c r="B79" s="17">
-        <f t="shared" si="0"/>
+      <c r="B79" s="16">
+        <f>ROW(B79) - ROW($B$7)</f>
         <v>72</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="D79" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="E79" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="F79" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="G79" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="H79" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="I79" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J79" s="20" t="s">
-        <v>413</v>
-      </c>
-      <c r="K79" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="L79" s="20">
+        <v>587</v>
+      </c>
+      <c r="D79" s="53" t="s">
+        <v>571</v>
+      </c>
+      <c r="E79" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="F79" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="G79" s="57" t="s">
+        <v>290</v>
+      </c>
+      <c r="H79" s="53" t="s">
+        <v>312</v>
+      </c>
+      <c r="I79" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J79" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="K79" s="57" t="s">
+        <v>429</v>
+      </c>
+      <c r="L79" s="45">
         <v>1</v>
       </c>
-      <c r="M79" s="20">
-        <f t="shared" ref="M79" si="70">L79*5</f>
+      <c r="M79" s="45">
+        <f t="shared" si="68"/>
         <v>5</v>
       </c>
-      <c r="N79" s="14">
-        <v>6</v>
-      </c>
-      <c r="O79" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P79" s="49" t="s">
-        <v>531</v>
-      </c>
-      <c r="Q79" s="21">
-        <f t="shared" ref="Q79" si="71">P79*N79</f>
-        <v>2.1852</v>
-      </c>
-      <c r="R79" s="20"/>
+      <c r="N79" s="45" t="s">
+        <v>464</v>
+      </c>
+      <c r="O79" s="49" t="s">
+        <v>474</v>
+      </c>
+      <c r="P79" s="50" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q79" s="51" t="s">
+        <v>464</v>
+      </c>
+      <c r="R79" s="48" t="s">
+        <v>556</v>
+      </c>
     </row>
     <row r="80" spans="1:18">
       <c r="A80" s="1"/>
-      <c r="B80" s="16">
-        <f>ROW(B80) - ROW($B$7)</f>
+      <c r="B80" s="17">
+        <f t="shared" si="0"/>
         <v>73</v>
       </c>
       <c r="C80" s="22" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>228</v>
+        <v>465</v>
       </c>
       <c r="G80" s="14" t="s">
-        <v>302</v>
+        <v>222</v>
       </c>
       <c r="H80" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="I80" s="55" t="s">
-        <v>561</v>
+        <v>336</v>
+      </c>
+      <c r="I80" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="K80" s="45" t="s">
-        <v>468</v>
+        <v>408</v>
+      </c>
+      <c r="K80" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L80" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80" s="14">
         <f>L80*5</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N80" s="14">
-        <v>6</v>
-      </c>
-      <c r="O80" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P80" s="49" t="s">
-        <v>532</v>
+        <v>15</v>
+      </c>
+      <c r="O80" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P80" s="46" t="s">
+        <v>526</v>
       </c>
       <c r="Q80" s="15">
         <f>P80*N80</f>
-        <v>2.5122</v>
+        <v>2.3280000000000003</v>
       </c>
       <c r="R80" s="14"/>
     </row>
     <row r="81" spans="1:18" ht="36">
       <c r="A81" s="1"/>
-      <c r="B81" s="17">
-        <f t="shared" si="0"/>
+      <c r="B81" s="16">
+        <f>ROW(B81) - ROW($B$7)</f>
         <v>74</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D81" s="20" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="F81" s="20" t="s">
-        <v>229</v>
+        <v>179</v>
+      </c>
+      <c r="F81" s="14" t="s">
+        <v>465</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>303</v>
+        <v>223</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="I81" s="55" t="s">
-        <v>561</v>
+        <v>337</v>
+      </c>
+      <c r="I81" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J81" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="K81" s="45" t="s">
-        <v>468</v>
+        <v>409</v>
+      </c>
+      <c r="K81" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L81" s="20">
         <v>1</v>
       </c>
       <c r="M81" s="20">
-        <f t="shared" ref="M81" si="72">L81*5</f>
+        <f t="shared" ref="M81" si="70">L81*5</f>
         <v>5</v>
       </c>
       <c r="N81" s="14">
-        <v>10</v>
-      </c>
-      <c r="O81" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P81" s="49" t="s">
-        <v>500</v>
+        <v>6</v>
+      </c>
+      <c r="O81" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P81" s="46" t="s">
+        <v>527</v>
       </c>
       <c r="Q81" s="21">
-        <f t="shared" ref="Q81" si="73">P81*N81</f>
-        <v>1.7290000000000001</v>
+        <f t="shared" ref="Q81" si="71">P81*N81</f>
+        <v>2.1852</v>
       </c>
       <c r="R81" s="20"/>
     </row>
     <row r="82" spans="1:18">
       <c r="A82" s="1"/>
-      <c r="B82" s="16">
-        <f>ROW(B82) - ROW($B$7)</f>
+      <c r="B82" s="17">
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>25</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="G82" s="14" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H82" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="I82" s="55" t="s">
-        <v>561</v>
+        <v>316</v>
+      </c>
+      <c r="I82" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J82" s="14" t="s">
-        <v>416</v>
-      </c>
-      <c r="K82" s="45" t="s">
-        <v>468</v>
+        <v>410</v>
+      </c>
+      <c r="K82" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L82" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M82" s="14">
         <f>L82*5</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N82" s="14">
-        <v>16</v>
-      </c>
-      <c r="O82" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P82" s="49" t="s">
-        <v>533</v>
+        <v>6</v>
+      </c>
+      <c r="O82" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P82" s="46" t="s">
+        <v>528</v>
       </c>
       <c r="Q82" s="15">
         <f>P82*N82</f>
-        <v>12.940799999999999</v>
+        <v>2.5122</v>
       </c>
       <c r="R82" s="14"/>
     </row>
-    <row r="83" spans="1:18">
+    <row r="83" spans="1:18" ht="36">
       <c r="A83" s="1"/>
-      <c r="B83" s="17">
-        <f t="shared" si="0"/>
+      <c r="B83" s="16">
+        <f>ROW(B83) - ROW($B$7)</f>
         <v>76</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D83" s="20" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="I83" s="55" t="s">
-        <v>561</v>
+        <v>338</v>
+      </c>
+      <c r="I83" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J83" s="20" t="s">
-        <v>417</v>
-      </c>
-      <c r="K83" s="45" t="s">
-        <v>468</v>
+        <v>411</v>
+      </c>
+      <c r="K83" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L83" s="20">
         <v>1</v>
       </c>
       <c r="M83" s="20">
-        <f t="shared" ref="M83" si="74">L83*5</f>
+        <f t="shared" ref="M83" si="72">L83*5</f>
         <v>5</v>
       </c>
       <c r="N83" s="14">
-        <v>6</v>
-      </c>
-      <c r="O83" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P83" s="49" t="s">
-        <v>534</v>
+        <v>10</v>
+      </c>
+      <c r="O83" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P83" s="46" t="s">
+        <v>496</v>
       </c>
       <c r="Q83" s="21">
-        <f t="shared" ref="Q83" si="75">P83*N83</f>
-        <v>16.179600000000001</v>
+        <f t="shared" ref="Q83" si="73">P83*N83</f>
+        <v>1.7290000000000001</v>
       </c>
       <c r="R83" s="20"/>
     </row>
     <row r="84" spans="1:18">
       <c r="A84" s="1"/>
-      <c r="B84" s="16">
-        <f>ROW(B84) - ROW($B$7)</f>
+      <c r="B84" s="17">
+        <f t="shared" si="0"/>
         <v>77</v>
       </c>
       <c r="C84" s="22" t="s">
         <v>25</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="G84" s="14" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H84" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="I84" s="55" t="s">
-        <v>561</v>
+        <v>339</v>
+      </c>
+      <c r="I84" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>418</v>
-      </c>
-      <c r="K84" s="45" t="s">
-        <v>468</v>
+        <v>412</v>
+      </c>
+      <c r="K84" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L84" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M84" s="14">
         <f>L84*5</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N84" s="14">
-        <v>6</v>
-      </c>
-      <c r="O84" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P84" s="49" t="s">
-        <v>535</v>
+        <v>16</v>
+      </c>
+      <c r="O84" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P84" s="46" t="s">
+        <v>529</v>
       </c>
       <c r="Q84" s="15">
         <f>P84*N84</f>
-        <v>4.6284000000000001</v>
+        <v>12.940799999999999</v>
       </c>
       <c r="R84" s="14"/>
     </row>
     <row r="85" spans="1:18">
       <c r="A85" s="1"/>
-      <c r="B85" s="17">
-        <f t="shared" si="0"/>
+      <c r="B85" s="16">
+        <f>ROW(B85) - ROW($B$7)</f>
         <v>78</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D85" s="20" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="I85" s="55" t="s">
-        <v>561</v>
+        <v>340</v>
+      </c>
+      <c r="I85" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J85" s="20" t="s">
-        <v>419</v>
-      </c>
-      <c r="K85" s="45" t="s">
-        <v>468</v>
+        <v>413</v>
+      </c>
+      <c r="K85" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L85" s="20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M85" s="20">
-        <f t="shared" ref="M85" si="76">L85*5</f>
-        <v>10</v>
+        <f t="shared" ref="M85" si="74">L85*5</f>
+        <v>5</v>
       </c>
       <c r="N85" s="14">
-        <v>11</v>
-      </c>
-      <c r="O85" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P85" s="49" t="s">
-        <v>536</v>
+        <v>6</v>
+      </c>
+      <c r="O85" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P85" s="46" t="s">
+        <v>530</v>
       </c>
       <c r="Q85" s="21">
-        <f t="shared" ref="Q85" si="77">P85*N85</f>
-        <v>27.9345</v>
+        <f t="shared" ref="Q85" si="75">P85*N85</f>
+        <v>16.179600000000001</v>
       </c>
       <c r="R85" s="20"/>
     </row>
     <row r="86" spans="1:18">
       <c r="A86" s="1"/>
-      <c r="B86" s="16">
-        <f>ROW(B86) - ROW($B$7)</f>
+      <c r="B86" s="17">
+        <f t="shared" si="0"/>
         <v>79</v>
       </c>
       <c r="C86" s="22" t="s">
         <v>25</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F86" s="14" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="G86" s="14" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="H86" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="I86" s="55" t="s">
-        <v>561</v>
+        <v>341</v>
+      </c>
+      <c r="I86" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="K86" s="45" t="s">
-        <v>468</v>
+        <v>414</v>
+      </c>
+      <c r="K86" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L86" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M86" s="14">
         <f>L86*5</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N86" s="14">
-        <v>11</v>
-      </c>
-      <c r="O86" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P86" s="49" t="s">
-        <v>537</v>
+        <v>6</v>
+      </c>
+      <c r="O86" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P86" s="46" t="s">
+        <v>531</v>
       </c>
       <c r="Q86" s="15">
         <f>P86*N86</f>
-        <v>32.843799999999995</v>
+        <v>4.6284000000000001</v>
       </c>
       <c r="R86" s="14"/>
     </row>
-    <row r="87" spans="1:18" ht="24">
+    <row r="87" spans="1:18">
       <c r="A87" s="1"/>
-      <c r="B87" s="17">
-        <f t="shared" si="0"/>
+      <c r="B87" s="16">
+        <f>ROW(B87) - ROW($B$7)</f>
         <v>80</v>
       </c>
       <c r="C87" s="23" t="s">
         <v>25</v>
       </c>
       <c r="D87" s="20" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>346</v>
-      </c>
-      <c r="I87" s="55" t="s">
-        <v>561</v>
+        <v>339</v>
+      </c>
+      <c r="I87" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J87" s="20" t="s">
-        <v>421</v>
-      </c>
-      <c r="K87" s="45" t="s">
-        <v>468</v>
+        <v>415</v>
+      </c>
+      <c r="K87" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L87" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M87" s="20">
-        <f t="shared" ref="M87" si="78">L87*5</f>
-        <v>5</v>
+        <f t="shared" ref="M87" si="76">L87*5</f>
+        <v>10</v>
       </c>
       <c r="N87" s="14">
-        <v>6</v>
-      </c>
-      <c r="O87" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P87" s="49" t="s">
-        <v>538</v>
+        <v>11</v>
+      </c>
+      <c r="O87" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P87" s="46" t="s">
+        <v>532</v>
       </c>
       <c r="Q87" s="21">
-        <f t="shared" ref="Q87" si="79">P87*N87</f>
-        <v>2.0244</v>
+        <f t="shared" ref="Q87" si="77">P87*N87</f>
+        <v>27.9345</v>
       </c>
       <c r="R87" s="20"/>
     </row>
     <row r="88" spans="1:18">
       <c r="A88" s="1"/>
-      <c r="B88" s="16">
-        <f>ROW(B88) - ROW($B$7)</f>
+      <c r="B88" s="17">
+        <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="C88" s="22" t="s">
         <v>25</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G88" s="14" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="H88" s="14" t="s">
-        <v>347</v>
-      </c>
-      <c r="I88" s="55" t="s">
-        <v>561</v>
+        <v>339</v>
+      </c>
+      <c r="I88" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>557</v>
-      </c>
-      <c r="K88" s="45" t="s">
-        <v>468</v>
+        <v>416</v>
+      </c>
+      <c r="K88" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L88" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M88" s="14">
         <f>L88*5</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N88" s="14">
-        <v>6</v>
-      </c>
-      <c r="O88" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P88" s="49" t="s">
-        <v>539</v>
+        <v>11</v>
+      </c>
+      <c r="O88" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P88" s="46" t="s">
+        <v>533</v>
       </c>
       <c r="Q88" s="15">
         <f>P88*N88</f>
-        <v>51.760199999999998</v>
+        <v>32.843799999999995</v>
       </c>
       <c r="R88" s="14"/>
     </row>
-    <row r="89" spans="1:18">
+    <row r="89" spans="1:18" ht="24">
       <c r="A89" s="1"/>
-      <c r="B89" s="17">
-        <f t="shared" si="0"/>
+      <c r="B89" s="16">
+        <f>ROW(B89) - ROW($B$7)</f>
         <v>82</v>
       </c>
-      <c r="C89" s="22" t="s">
+      <c r="C89" s="23" t="s">
         <v>25</v>
       </c>
       <c r="D89" s="20" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="F89" s="14" t="s">
-        <v>470</v>
+        <v>187</v>
+      </c>
+      <c r="F89" s="20" t="s">
+        <v>231</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>237</v>
+        <v>305</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="I89" s="55" t="s">
-        <v>561</v>
+        <v>342</v>
+      </c>
+      <c r="I89" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J89" s="20" t="s">
-        <v>558</v>
-      </c>
-      <c r="K89" s="45" t="s">
-        <v>468</v>
+        <v>417</v>
+      </c>
+      <c r="K89" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L89" s="20">
         <v>1</v>
       </c>
       <c r="M89" s="20">
-        <f t="shared" ref="M89" si="80">L89*5</f>
+        <f t="shared" ref="M89" si="78">L89*5</f>
         <v>5</v>
       </c>
       <c r="N89" s="14">
         <v>6</v>
       </c>
-      <c r="O89" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P89" s="49" t="s">
-        <v>540</v>
+      <c r="O89" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P89" s="46" t="s">
+        <v>534</v>
       </c>
       <c r="Q89" s="21">
-        <f t="shared" ref="Q89" si="81">P89*N89</f>
-        <v>2.7401999999999997</v>
+        <f t="shared" ref="Q89" si="79">P89*N89</f>
+        <v>2.0244</v>
       </c>
       <c r="R89" s="20"/>
     </row>
-    <row r="90" spans="1:18" ht="24">
+    <row r="90" spans="1:18">
       <c r="A90" s="1"/>
-      <c r="B90" s="16">
-        <f>ROW(B90) - ROW($B$7)</f>
+      <c r="B90" s="17">
+        <f t="shared" si="0"/>
         <v>83</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D90" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="E90" s="48" t="s">
-        <v>194</v>
-      </c>
-      <c r="F90" s="48" t="s">
-        <v>238</v>
-      </c>
-      <c r="G90" s="48" t="s">
-        <v>311</v>
-      </c>
-      <c r="H90" s="48" t="s">
-        <v>348</v>
-      </c>
-      <c r="I90" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J90" s="48" t="s">
-        <v>422</v>
-      </c>
-      <c r="K90" s="47" t="s">
-        <v>433</v>
-      </c>
-      <c r="L90" s="48">
+        <v>25</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="F90" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="G90" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="H90" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="I90" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J90" s="14" t="s">
+        <v>553</v>
+      </c>
+      <c r="K90" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L90" s="14">
         <v>1</v>
       </c>
-      <c r="M90" s="48">
+      <c r="M90" s="14">
         <f>L90*5</f>
         <v>5</v>
       </c>
-      <c r="N90" s="48" t="s">
-        <v>468</v>
-      </c>
-      <c r="O90" s="52" t="s">
-        <v>478</v>
-      </c>
-      <c r="P90" s="53" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q90" s="54" t="s">
-        <v>468</v>
-      </c>
-      <c r="R90" s="51" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" ht="24">
+      <c r="N90" s="14">
+        <v>6</v>
+      </c>
+      <c r="O90" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P90" s="46" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q90" s="15">
+        <f>P90*N90</f>
+        <v>51.760199999999998</v>
+      </c>
+      <c r="R90" s="14"/>
+    </row>
+    <row r="91" spans="1:18">
       <c r="A91" s="1"/>
-      <c r="B91" s="17">
-        <f t="shared" si="0"/>
+      <c r="B91" s="16">
+        <f>ROW(B91) - ROW($B$7)</f>
         <v>84</v>
       </c>
-      <c r="C91" s="23" t="s">
-        <v>27</v>
+      <c r="C91" s="22" t="s">
+        <v>25</v>
       </c>
       <c r="D91" s="20" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>312</v>
+        <v>233</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>349</v>
-      </c>
-      <c r="I91" s="55" t="s">
-        <v>561</v>
+        <v>319</v>
+      </c>
+      <c r="I91" s="52" t="s">
+        <v>557</v>
       </c>
       <c r="J91" s="20" t="s">
-        <v>423</v>
-      </c>
-      <c r="K91" s="46" t="s">
-        <v>461</v>
+        <v>554</v>
+      </c>
+      <c r="K91" s="42" t="s">
+        <v>464</v>
       </c>
       <c r="L91" s="20">
         <v>1</v>
       </c>
       <c r="M91" s="20">
-        <f t="shared" ref="M91" si="82">L91*5</f>
+        <f t="shared" ref="M91" si="80">L91*5</f>
         <v>5</v>
       </c>
       <c r="N91" s="14">
-        <v>10</v>
-      </c>
-      <c r="O91" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P91" s="49" t="s">
-        <v>541</v>
+        <v>6</v>
+      </c>
+      <c r="O91" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P91" s="46" t="s">
+        <v>536</v>
       </c>
       <c r="Q91" s="21">
-        <f t="shared" ref="Q91" si="83">P91*N91</f>
-        <v>3.008</v>
+        <f t="shared" ref="Q91" si="81">P91*N91</f>
+        <v>2.7401999999999997</v>
       </c>
       <c r="R91" s="20"/>
     </row>
-    <row r="92" spans="1:18" ht="24.75" thickBot="1">
+    <row r="92" spans="1:18" ht="24">
       <c r="A92" s="1"/>
-      <c r="B92" s="16">
-        <f>ROW(B92) - ROW($B$7)</f>
+      <c r="B92" s="17">
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="C92" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D92" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E92" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="F92" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="G92" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="H92" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="I92" s="55" t="s">
-        <v>561</v>
-      </c>
-      <c r="J92" s="14" t="s">
-        <v>424</v>
-      </c>
-      <c r="K92" s="45" t="s">
-        <v>462</v>
-      </c>
-      <c r="L92" s="14">
+      <c r="D92" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="E92" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="F92" s="45" t="s">
+        <v>234</v>
+      </c>
+      <c r="G92" s="45" t="s">
+        <v>307</v>
+      </c>
+      <c r="H92" s="45" t="s">
+        <v>344</v>
+      </c>
+      <c r="I92" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J92" s="45" t="s">
+        <v>418</v>
+      </c>
+      <c r="K92" s="44" t="s">
+        <v>429</v>
+      </c>
+      <c r="L92" s="45">
         <v>1</v>
       </c>
-      <c r="M92" s="14">
+      <c r="M92" s="45">
         <f>L92*5</f>
         <v>5</v>
       </c>
-      <c r="N92" s="14" t="s">
-        <v>545</v>
-      </c>
-      <c r="O92" s="50" t="s">
-        <v>478</v>
-      </c>
-      <c r="P92" s="49" t="s">
-        <v>542</v>
-      </c>
-      <c r="Q92" s="15">
-        <f>P92*N92</f>
+      <c r="N92" s="45" t="s">
+        <v>464</v>
+      </c>
+      <c r="O92" s="49" t="s">
+        <v>474</v>
+      </c>
+      <c r="P92" s="50" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q92" s="51" t="s">
+        <v>464</v>
+      </c>
+      <c r="R92" s="48" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="24">
+      <c r="A93" s="1"/>
+      <c r="B93" s="16">
+        <f>ROW(B93) - ROW($B$7)</f>
+        <v>86</v>
+      </c>
+      <c r="C93" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D93" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E93" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F93" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="G93" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="H93" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="I93" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J93" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="K93" s="43" t="s">
+        <v>457</v>
+      </c>
+      <c r="L93" s="20">
+        <v>1</v>
+      </c>
+      <c r="M93" s="20">
+        <f t="shared" ref="M93" si="82">L93*5</f>
+        <v>5</v>
+      </c>
+      <c r="N93" s="14">
+        <v>10</v>
+      </c>
+      <c r="O93" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P93" s="46" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q93" s="21">
+        <f t="shared" ref="Q93" si="83">P93*N93</f>
+        <v>3.008</v>
+      </c>
+      <c r="R93" s="20"/>
+    </row>
+    <row r="94" spans="1:18" ht="24">
+      <c r="A94" s="1"/>
+      <c r="B94" s="16">
+        <f t="shared" ref="B94:B99" si="84">ROW(B94) - ROW($B$7)</f>
+        <v>87</v>
+      </c>
+      <c r="C94" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D94" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E94" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="F94" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="G94" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="H94" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="I94" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J94" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="K94" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="L94" s="14">
+        <v>1</v>
+      </c>
+      <c r="M94" s="14">
+        <f>L94*5</f>
+        <v>5</v>
+      </c>
+      <c r="N94" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="O94" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P94" s="46" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q94" s="15">
+        <f>P94*N94</f>
         <v>0.65600000000000003</v>
       </c>
-      <c r="R92" s="14"/>
-    </row>
-    <row r="93" spans="1:18" ht="19.5" thickBot="1">
-      <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1"/>
-      <c r="K93" s="1"/>
-      <c r="L93" s="1"/>
-      <c r="M93" s="1"/>
-      <c r="N93" s="43" t="s">
+      <c r="R94" s="14"/>
+    </row>
+    <row r="95" spans="1:18">
+      <c r="A95" s="1"/>
+      <c r="B95" s="16">
+        <f t="shared" si="84"/>
+        <v>88</v>
+      </c>
+      <c r="C95" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>572</v>
+      </c>
+      <c r="E95" s="42" t="s">
+        <v>573</v>
+      </c>
+      <c r="F95" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="G95" s="42" t="s">
+        <v>574</v>
+      </c>
+      <c r="H95" s="14" t="s">
+        <v>575</v>
+      </c>
+      <c r="I95" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J95" s="14" t="s">
+        <v>589</v>
+      </c>
+      <c r="K95" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L95" s="14">
+        <v>5</v>
+      </c>
+      <c r="M95" s="14">
+        <f t="shared" ref="M95:M99" si="85">L95*5</f>
+        <v>25</v>
+      </c>
+      <c r="N95" s="14">
+        <v>40</v>
+      </c>
+      <c r="O95" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P95" s="46">
+        <v>2.01E-2</v>
+      </c>
+      <c r="Q95" s="15">
+        <f t="shared" ref="Q95:Q99" si="86">P95*N95</f>
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="R95" s="14"/>
+    </row>
+    <row r="96" spans="1:18" ht="24">
+      <c r="A96" s="1"/>
+      <c r="B96" s="16">
+        <f t="shared" si="84"/>
+        <v>89</v>
+      </c>
+      <c r="C96" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="42" t="s">
+        <v>576</v>
+      </c>
+      <c r="F96" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="G96" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="H96" s="14" t="s">
+        <v>578</v>
+      </c>
+      <c r="I96" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J96" s="14" t="s">
+        <v>590</v>
+      </c>
+      <c r="K96" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L96" s="14">
+        <v>1</v>
+      </c>
+      <c r="M96" s="14">
+        <f t="shared" si="85"/>
+        <v>5</v>
+      </c>
+      <c r="N96" s="14">
+        <v>5</v>
+      </c>
+      <c r="O96" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P96" s="46">
+        <v>8.6199999999999999E-2</v>
+      </c>
+      <c r="Q96" s="15">
+        <f t="shared" si="86"/>
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="R96" s="14"/>
+    </row>
+    <row r="97" spans="1:18" ht="24">
+      <c r="A97" s="1"/>
+      <c r="B97" s="16">
+        <f t="shared" si="84"/>
+        <v>90</v>
+      </c>
+      <c r="C97" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="D97" s="14" t="s">
+        <v>579</v>
+      </c>
+      <c r="E97" s="42" t="s">
+        <v>580</v>
+      </c>
+      <c r="F97" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="G97" s="42">
+        <v>50173</v>
+      </c>
+      <c r="H97" s="14" t="s">
+        <v>581</v>
+      </c>
+      <c r="I97" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J97" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="K97" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L97" s="14">
+        <v>1</v>
+      </c>
+      <c r="M97" s="14">
+        <f t="shared" si="85"/>
+        <v>5</v>
+      </c>
+      <c r="N97" s="14">
+        <v>5</v>
+      </c>
+      <c r="O97" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P97" s="46">
+        <v>1.3977999999999999</v>
+      </c>
+      <c r="Q97" s="15">
+        <f t="shared" si="86"/>
+        <v>6.9889999999999999</v>
+      </c>
+      <c r="R97" s="14"/>
+    </row>
+    <row r="98" spans="1:18">
+      <c r="A98" s="1"/>
+      <c r="B98" s="16">
+        <f t="shared" si="84"/>
+        <v>91</v>
+      </c>
+      <c r="C98" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="E98" s="42" t="s">
+        <v>582</v>
+      </c>
+      <c r="F98" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="G98" s="42" t="s">
+        <v>583</v>
+      </c>
+      <c r="H98" s="14" t="s">
+        <v>584</v>
+      </c>
+      <c r="I98" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J98" s="14" t="s">
+        <v>592</v>
+      </c>
+      <c r="K98" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L98" s="14">
+        <v>8</v>
+      </c>
+      <c r="M98" s="14">
+        <f t="shared" si="85"/>
+        <v>40</v>
+      </c>
+      <c r="N98" s="14">
+        <v>40</v>
+      </c>
+      <c r="O98" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P98" s="46">
+        <v>0.13730000000000001</v>
+      </c>
+      <c r="Q98" s="15">
+        <f t="shared" si="86"/>
+        <v>5.492</v>
+      </c>
+      <c r="R98" s="14"/>
+    </row>
+    <row r="99" spans="1:18" ht="15.75" thickBot="1">
+      <c r="A99" s="1"/>
+      <c r="B99" s="16">
+        <f t="shared" si="84"/>
+        <v>92</v>
+      </c>
+      <c r="C99" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="E99" s="42" t="s">
+        <v>582</v>
+      </c>
+      <c r="F99" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="G99" s="42" t="s">
+        <v>585</v>
+      </c>
+      <c r="H99" s="14" t="s">
+        <v>584</v>
+      </c>
+      <c r="I99" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="J99" s="14"/>
+      <c r="K99" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L99" s="14">
+        <v>4</v>
+      </c>
+      <c r="M99" s="14">
+        <f t="shared" si="85"/>
+        <v>20</v>
+      </c>
+      <c r="N99" s="14">
+        <v>20</v>
+      </c>
+      <c r="O99" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="P99" s="46">
+        <v>8.8099999999999998E-2</v>
+      </c>
+      <c r="Q99" s="15">
+        <f t="shared" si="86"/>
+        <v>1.762</v>
+      </c>
+      <c r="R99" s="14"/>
+    </row>
+    <row r="100" spans="1:18" ht="19.5" thickBot="1">
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+      <c r="N100" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="O93" s="44"/>
-      <c r="P93" s="44"/>
-      <c r="Q93" s="18">
-        <f>SUM(Q8:Q92)</f>
-        <v>242.62689999999998</v>
-      </c>
-      <c r="R93" s="1"/>
-    </row>
-    <row r="94" spans="1:18" ht="19.5" thickBot="1">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1"/>
-      <c r="K94" s="1"/>
-      <c r="L94" s="1"/>
-      <c r="M94" s="1"/>
-      <c r="N94" s="43" t="s">
+      <c r="O100" s="56"/>
+      <c r="P100" s="56"/>
+      <c r="Q100" s="18">
+        <f>SUM(Q8:Q99)</f>
+        <v>257.0924</v>
+      </c>
+      <c r="R100" s="1"/>
+    </row>
+    <row r="101" spans="1:18" ht="19.5" thickBot="1">
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1"/>
+      <c r="N101" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="O94" s="44"/>
-      <c r="P94" s="44"/>
-      <c r="Q94" s="19">
-        <f>Q93/5</f>
-        <v>48.525379999999998</v>
-      </c>
-      <c r="R94" s="1"/>
-    </row>
-    <row r="106" spans="13:13">
-      <c r="M106" s="38"/>
+      <c r="O101" s="56"/>
+      <c r="P101" s="56"/>
+      <c r="Q101" s="19">
+        <f>Q100/5</f>
+        <v>51.418480000000002</v>
+      </c>
+      <c r="R101" s="1"/>
+    </row>
+    <row r="113" spans="13:13">
+      <c r="M113" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="N101:P101"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O8" r:id="rId1"/>
@@ -7522,68 +7987,75 @@
     <hyperlink ref="O31" r:id="rId23"/>
     <hyperlink ref="O32" r:id="rId24"/>
     <hyperlink ref="O33" r:id="rId25"/>
-    <hyperlink ref="O34" r:id="rId26"/>
-    <hyperlink ref="O35" r:id="rId27"/>
-    <hyperlink ref="O36" r:id="rId28"/>
-    <hyperlink ref="O37" r:id="rId29"/>
-    <hyperlink ref="O38" r:id="rId30"/>
-    <hyperlink ref="O40" r:id="rId31"/>
-    <hyperlink ref="O41" r:id="rId32"/>
-    <hyperlink ref="O42" r:id="rId33"/>
-    <hyperlink ref="O43" r:id="rId34"/>
-    <hyperlink ref="O44" r:id="rId35"/>
-    <hyperlink ref="O45" r:id="rId36"/>
-    <hyperlink ref="O46" r:id="rId37"/>
-    <hyperlink ref="O47" r:id="rId38"/>
-    <hyperlink ref="O49" r:id="rId39"/>
-    <hyperlink ref="O50" r:id="rId40"/>
-    <hyperlink ref="O51" r:id="rId41"/>
-    <hyperlink ref="O52" r:id="rId42"/>
-    <hyperlink ref="O53" r:id="rId43"/>
-    <hyperlink ref="O54" r:id="rId44"/>
-    <hyperlink ref="O55" r:id="rId45"/>
-    <hyperlink ref="O56" r:id="rId46"/>
-    <hyperlink ref="O57" r:id="rId47"/>
-    <hyperlink ref="O58" r:id="rId48"/>
-    <hyperlink ref="O59" r:id="rId49"/>
-    <hyperlink ref="O61" r:id="rId50"/>
-    <hyperlink ref="O62" r:id="rId51"/>
-    <hyperlink ref="O63" r:id="rId52"/>
-    <hyperlink ref="O65" r:id="rId53"/>
-    <hyperlink ref="O66" r:id="rId54"/>
-    <hyperlink ref="O68" r:id="rId55"/>
-    <hyperlink ref="O69" r:id="rId56"/>
-    <hyperlink ref="O70" r:id="rId57"/>
-    <hyperlink ref="O71" r:id="rId58"/>
-    <hyperlink ref="O72" r:id="rId59"/>
-    <hyperlink ref="O74" r:id="rId60"/>
-    <hyperlink ref="O75" r:id="rId61"/>
-    <hyperlink ref="O76" r:id="rId62"/>
-    <hyperlink ref="O77" r:id="rId63"/>
-    <hyperlink ref="O78" r:id="rId64"/>
-    <hyperlink ref="O79" r:id="rId65"/>
-    <hyperlink ref="O80" r:id="rId66"/>
-    <hyperlink ref="O81" r:id="rId67"/>
-    <hyperlink ref="O82" r:id="rId68"/>
-    <hyperlink ref="O83" r:id="rId69"/>
-    <hyperlink ref="O84" r:id="rId70"/>
-    <hyperlink ref="O85" r:id="rId71"/>
-    <hyperlink ref="O86" r:id="rId72"/>
-    <hyperlink ref="O87" r:id="rId73"/>
-    <hyperlink ref="O88" r:id="rId74"/>
-    <hyperlink ref="O89" r:id="rId75"/>
-    <hyperlink ref="O90" r:id="rId76"/>
-    <hyperlink ref="O91" r:id="rId77"/>
-    <hyperlink ref="O92" r:id="rId78"/>
-    <hyperlink ref="O48" r:id="rId79"/>
-    <hyperlink ref="O67" r:id="rId80"/>
-    <hyperlink ref="O64" r:id="rId81"/>
-    <hyperlink ref="O73" r:id="rId82"/>
-    <hyperlink ref="O60" r:id="rId83"/>
+    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O36" r:id="rId27"/>
+    <hyperlink ref="O37" r:id="rId28"/>
+    <hyperlink ref="O38" r:id="rId29"/>
+    <hyperlink ref="O39" r:id="rId30"/>
+    <hyperlink ref="O41" r:id="rId31"/>
+    <hyperlink ref="O42" r:id="rId32"/>
+    <hyperlink ref="O43" r:id="rId33"/>
+    <hyperlink ref="O44" r:id="rId34"/>
+    <hyperlink ref="O45" r:id="rId35"/>
+    <hyperlink ref="O46" r:id="rId36"/>
+    <hyperlink ref="O47" r:id="rId37"/>
+    <hyperlink ref="O48" r:id="rId38"/>
+    <hyperlink ref="O50" r:id="rId39"/>
+    <hyperlink ref="O51" r:id="rId40"/>
+    <hyperlink ref="O52" r:id="rId41"/>
+    <hyperlink ref="O53" r:id="rId42"/>
+    <hyperlink ref="O54" r:id="rId43"/>
+    <hyperlink ref="O55" r:id="rId44"/>
+    <hyperlink ref="O56" r:id="rId45"/>
+    <hyperlink ref="O57" r:id="rId46"/>
+    <hyperlink ref="O58" r:id="rId47"/>
+    <hyperlink ref="O59" r:id="rId48"/>
+    <hyperlink ref="O60" r:id="rId49"/>
+    <hyperlink ref="O62" r:id="rId50"/>
+    <hyperlink ref="O63" r:id="rId51"/>
+    <hyperlink ref="O64" r:id="rId52"/>
+    <hyperlink ref="O66" r:id="rId53"/>
+    <hyperlink ref="O67" r:id="rId54"/>
+    <hyperlink ref="O69" r:id="rId55"/>
+    <hyperlink ref="O70" r:id="rId56"/>
+    <hyperlink ref="O71" r:id="rId57"/>
+    <hyperlink ref="O72" r:id="rId58"/>
+    <hyperlink ref="O73" r:id="rId59"/>
+    <hyperlink ref="O75" r:id="rId60"/>
+    <hyperlink ref="O76" r:id="rId61"/>
+    <hyperlink ref="O77" r:id="rId62"/>
+    <hyperlink ref="O78" r:id="rId63"/>
+    <hyperlink ref="O80" r:id="rId64"/>
+    <hyperlink ref="O81" r:id="rId65"/>
+    <hyperlink ref="O82" r:id="rId66"/>
+    <hyperlink ref="O83" r:id="rId67"/>
+    <hyperlink ref="O84" r:id="rId68"/>
+    <hyperlink ref="O85" r:id="rId69"/>
+    <hyperlink ref="O86" r:id="rId70"/>
+    <hyperlink ref="O87" r:id="rId71"/>
+    <hyperlink ref="O88" r:id="rId72"/>
+    <hyperlink ref="O89" r:id="rId73"/>
+    <hyperlink ref="O90" r:id="rId74"/>
+    <hyperlink ref="O91" r:id="rId75"/>
+    <hyperlink ref="O92" r:id="rId76"/>
+    <hyperlink ref="O93" r:id="rId77"/>
+    <hyperlink ref="O94" r:id="rId78"/>
+    <hyperlink ref="O49" r:id="rId79"/>
+    <hyperlink ref="O68" r:id="rId80"/>
+    <hyperlink ref="O65" r:id="rId81"/>
+    <hyperlink ref="O74" r:id="rId82"/>
+    <hyperlink ref="O61" r:id="rId83"/>
     <hyperlink ref="O16" r:id="rId84"/>
-    <hyperlink ref="O39" r:id="rId85"/>
+    <hyperlink ref="O40" r:id="rId85"/>
+    <hyperlink ref="O34" r:id="rId86"/>
+    <hyperlink ref="O79" r:id="rId87"/>
+    <hyperlink ref="O95" r:id="rId88"/>
+    <hyperlink ref="O96" r:id="rId89"/>
+    <hyperlink ref="O97" r:id="rId90"/>
+    <hyperlink ref="O98" r:id="rId91"/>
+    <hyperlink ref="O99" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId86"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId93"/>
 </worksheet>
 </file>